--- a/docs/homologacao/checklist_homologacao_operacional.xlsx
+++ b/docs/homologacao/checklist_homologacao_operacional.xlsx
@@ -14,17 +14,17 @@
   <calcPr iterateDelta="0.0001"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1777598330" val="1230" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1777598330" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1777598330" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1777598330"/>
+      <pm:revision xmlns:pm="smNativeData" day="1778271503" val="1230" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1778271503" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1778271503" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1778271503"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="562">
   <si>
     <t>✦  Checklist de Homologação Operacional — CSPdv</t>
   </si>
@@ -980,6 +980,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>Aumentar o tamanho da coluna de vigencia</t>
   </si>
   <si>
@@ -995,6 +1001,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>PROMOCOES</t>
   </si>
   <si>
@@ -1007,6 +1019,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>PROMOCOES</t>
   </si>
   <si>
@@ -1019,6 +1037,12 @@
     <t>Media</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>PROMOCOES</t>
   </si>
   <si>
@@ -1031,6 +1055,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>Ajustar preço após vinculação.</t>
   </si>
   <si>
@@ -1046,6 +1076,12 @@
     <t>Media</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>FINANCEIRO</t>
   </si>
   <si>
@@ -1058,6 +1094,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>FINANCEIRO</t>
   </si>
   <si>
@@ -1070,6 +1112,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>Aumentar altura do modal de abertura</t>
   </si>
   <si>
@@ -1085,6 +1133,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>FINANCEIRO</t>
   </si>
   <si>
@@ -1097,6 +1151,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>FINANCEIRO</t>
   </si>
   <si>
@@ -1109,6 +1169,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>FINANCEIRO</t>
   </si>
   <si>
@@ -1121,6 +1187,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>FINANCEIRO</t>
   </si>
   <si>
@@ -1133,6 +1205,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>FINANCEIRO</t>
   </si>
   <si>
@@ -1145,6 +1223,12 @@
     <t>Media</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>Mudar status da venda para Reembolsada</t>
   </si>
   <si>
@@ -1160,6 +1244,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>VENDA RAPIDA</t>
   </si>
   <si>
@@ -1172,6 +1262,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>VENDA RAPIDA</t>
   </si>
   <si>
@@ -1184,6 +1280,12 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>VENDAS E CAIXA</t>
   </si>
   <si>
@@ -1196,6 +1298,12 @@
     <t>Media</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
     <t>ESTOQUE</t>
   </si>
   <si>
@@ -1208,6 +1316,342 @@
     <t>Media</t>
   </si>
   <si>
+    <t>Aprovado</t>
+  </si>
+  <si>
+    <t>Iury</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Salvar Razão Social e verificar propagação</t>
+  </si>
+  <si>
+    <t>O nome da empresa salvo deve aparecer no cabeçalho do sistema, cupons e relatórios sem necessidade de reiniciar.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Selecionar PDV Padrão e confirmar vínculo</t>
+  </si>
+  <si>
+    <t>O PDV escolhido deve ser pré-selecionado ao abrir caixa e em novas operações, sem exigir seleção manual.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Alterar Moeda e verificar exibição nos módulos</t>
+  </si>
+  <si>
+    <t>Todos os valores exibidos no sistema (vendas, caixa, estoque) devem adotar o símbolo e formato da moeda configurada.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Definir Cliente Padrão e abrir nova venda</t>
+  </si>
+  <si>
+    <t>O cliente configurado deve ser pré-preenchido automaticamente ao iniciar uma venda rápida ou cupom.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Configurar Regra de Desconto como 'Permitir desconto manual'</t>
+  </si>
+  <si>
+    <t>O campo de desconto deve estar habilitado no cupom e aceitar valor digitado pelo operador sem erro.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Desativar Venda Rápida no painel admin e verificar ocultação</t>
+  </si>
+  <si>
+    <t>O botão ou acesso à Venda Rápida no painel administrativo deve desaparecer imediatamente após salvar.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Ativar 'Permitir venda sem estoque' e tentar vender produto zerado</t>
+  </si>
+  <si>
+    <t>A venda deve ser concluída normalmente mesmo com saldo de estoque igual a zero, sem bloqueio ou aviso impeditivo.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Configurar Fundo Inicial Sugerido e abrir caixa</t>
+  </si>
+  <si>
+    <t>O valor configurado deve ser pré-preenchido no campo de fundo ao abrir caixa, podendo ser alterado pelo operador.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Ativar 'Exigir admin em sangria' e executar sangria sem admin</t>
+  </si>
+  <si>
+    <t>O sistema deve solicitar senha de administrador antes de concluir a sangria, bloqueando a operação sem autenticação.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Ativar 'Exigir admin em reembolso' e tentar reembolso sem admin</t>
+  </si>
+  <si>
+    <t>O reembolso deve ser bloqueado até que credencial de administrador seja fornecida e validada.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Ativar 'Exigir admin em diferença no fechamento' e fechar com diferença</t>
+  </si>
+  <si>
+    <t>Ao detectar diferença no fechamento, o sistema deve exigir autenticação admin antes de registrar o fechamento.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Alterar Prioridade Promocional para 'Desconto manual antes da promoção'</t>
+  </si>
+  <si>
+    <t>Em vendas com promoção ativa e desconto manual aplicado, o desconto manual deve prevalecer sobre a campanha.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Ativar 'Bloquear promoções simultâneas por produto'</t>
+  </si>
+  <si>
+    <t>Se um produto elegível a duas campanhas for adicionado ao cupom, apenas uma promoção deve ser aplicada.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Ativar 'Promoções automáticas pela vigência' e checar campanha vigente</t>
+  </si>
+  <si>
+    <t>Uma promoção com data de início no passado e fim no futuro deve ser ativada automaticamente sem ação manual.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Configurar Horas de Sessão Persistida e aguardar expiração</t>
+  </si>
+  <si>
+    <t>Após o tempo configurado sem atividade, o sistema deve encerrar a sessão e redirecionar para o login.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Ativar 'Restaurar login automaticamente quando válido'</t>
+  </si>
+  <si>
+    <t>Ao reabrir o sistema dentro do período de sessão válido, o usuário deve ser autenticado sem digitar credenciais.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Ativar 'Bloquear fechamento com caixa aberto' e tentar fechar</t>
+  </si>
+  <si>
+    <t>O sistema deve impedir o encerramento do programa enquanto houver caixa aberto, exibindo aviso claro ao usuário.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Configurar Intervalo de Backup e verificar agendamento</t>
+  </si>
+  <si>
+    <t>O backup automático deve ocorrer dentro do intervalo configurado em horas, sem intervenção manual.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Alterar Perfil de Log e verificar nível de detalhamento</t>
+  </si>
+  <si>
+    <t>Os logs gerados devem corresponder ao perfil selecionado: 'Operacional' deve registrar operações sem dados de debug.</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Executar 'Backup agora' e verificar timestamp atualizado</t>
+  </si>
+  <si>
+    <t>Após clicar em 'Executar backup agora', o campo 'Último Backup Realizado' deve exibir data e hora atuais.</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Clicar em 'Abrir pasta de backups' e confirmar abertura</t>
+  </si>
+  <si>
+    <t>O explorador de arquivos deve abrir diretamente na pasta de destino dos backups configurada no sistema.</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>CONFIG. SISTEMA</t>
+  </si>
+  <si>
+    <t>Clicar em 'Copiar caminho do último backup' e colar em editor</t>
+  </si>
+  <si>
+    <t>O caminho completo do arquivo de backup mais recente deve ser copiado para a área de transferência sem erro.</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
     <t>Apoio da Homologacao</t>
   </si>
   <si>
@@ -1221,9 +1665,6 @@
   </si>
   <si>
     <t>Uso sugerido</t>
-  </si>
-  <si>
-    <t>Pendente</t>
   </si>
   <si>
     <t>Cenario ainda nao executado.</t>
@@ -1284,14 +1725,14 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0\ _R_$_-;\-* #,##0\ _R_$_-;_-* &quot;-&quot;\ _R_$_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;R$&quot;_-;\-* #,##0.00\ &quot;R$&quot;_-;_-* &quot;-&quot;??\ &quot;R$&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _R_$_-;\-* #,##0.00\ _R_$_-;_-* &quot;-&quot;??\ _R_$_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="165" formatCode="_-_R_$* #,##0.00_ ;_-_R_$* \-#,##0.00\ ;_-_R_$* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="166" formatCode="_-_R_$* #,##0_ ;_-_R_$* \-#,##0\ ;_-_R_$* &quot;-&quot;_ ;_-@_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;R$&quot;* #,##0.00_ ;_-&quot;R$&quot;* \-#,##0.00\ ;_-&quot;R$&quot;* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="168" formatCode="_-&quot;R$&quot;* #,##0_ ;_-&quot;R$&quot;* \-#,##0\ ;_-&quot;R$&quot;* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="164" formatCode="_-_R_$* #,##0.00_ ;_-_R_$* \-#,##0.00\ ;_-_R_$* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="165" formatCode="_-_R_$* #,##0_ ;_-_R_$* \-#,##0\ ;_-_R_$* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;* #,##0.00_ ;_-&quot;R$&quot;* \-#,##0.00\ ;_-&quot;R$&quot;* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="167" formatCode="_-&quot;R$&quot;* #,##0_ ;_-&quot;R$&quot;* \-#,##0\ ;_-&quot;R$&quot;* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="168" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="9" formatCode="0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1299,7 +1740,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -1314,7 +1755,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -1330,7 +1771,7 @@
       <sz val="16"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="320" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="320" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="320" lang="default" weight="bold"/>
@@ -1346,7 +1787,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="A8B8D8" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="A8B8D8" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" i="1"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" i="1"/>
             <pm:ea face="SimSun" sz="180" lang="default" i="1"/>
@@ -1362,7 +1803,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="1B2A4A" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1B2A4A" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
@@ -1378,7 +1819,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="2E7D32" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="2E7D32" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
@@ -1394,7 +1835,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="C62828" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="C62828" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
@@ -1410,7 +1851,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="6A1B9A" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="6A1B9A" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
@@ -1426,7 +1867,7 @@
       <sz val="20"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="400" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="400" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="400" lang="default" weight="bold"/>
@@ -1442,7 +1883,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="200" lang="default" weight="bold"/>
@@ -1458,7 +1899,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="6B7A99" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="6B7A99" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -1474,7 +1915,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="1B2A4A" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1B2A4A" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -1489,7 +1930,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="1B2A4A" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1B2A4A" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default"/>
             <pm:cs face="Times New Roman" sz="180" lang="default"/>
             <pm:ea face="SimSun" sz="180" lang="default"/>
@@ -1505,7 +1946,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="5C6880" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="5C6880" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default" i="1"/>
             <pm:cs face="Times New Roman" sz="160" lang="default" i="1"/>
             <pm:ea face="SimSun" sz="160" lang="default" i="1"/>
@@ -1521,7 +1962,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="C62828" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="C62828" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -1537,7 +1978,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="2E7D32" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="2E7D32" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -1552,7 +1993,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="5C6880" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="5C6880" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="160" lang="default"/>
             <pm:cs face="Times New Roman" sz="160" lang="default"/>
             <pm:ea face="SimSun" sz="160" lang="default"/>
@@ -1568,7 +2009,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="E65100" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="E65100" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -1584,7 +2025,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="1976D2" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1976D2" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
@@ -1600,7 +2041,7 @@
       <sz val="13"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="260" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="260" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="260" lang="default" weight="bold"/>
@@ -1616,7 +2057,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1777598330" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
@@ -1624,8 +2065,24 @@
         </ext>
       </extLst>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b/>
+      <color rgb="FFF59E0B"/>
+      <sz val="9"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="F59E0B" ulstyle="none" kern="1">
+            <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1638,7 +2095,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="001B2A4A" bgLvl="0" bgClr="00243657"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="001B2A4A" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1649,7 +2106,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00243657" bgLvl="0" bgClr="00123A63"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00243657" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1660,7 +2117,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00EEF1F8" bgLvl="0" bgClr="00F5F6FA"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00EEF1F8" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1671,7 +2128,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00F5F6FA"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1682,7 +2139,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00C8E6C9" bgLvl="0" bgClr="00D8DCE6"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00C8E6C9" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1693,7 +2150,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00FFCDD2" bgLvl="0" bgClr="00E1BEE7"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFCDD2" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1704,7 +2161,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00E1BEE7" bgLvl="0" bgClr="00FFCDD2"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E1BEE7" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1715,7 +2172,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="002E7D32" bgLvl="0" bgClr="000F7B6C"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="002E7D32" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1726,7 +2183,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00C62828" bgLvl="0" bgClr="00993366"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00C62828" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1737,7 +2194,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="006A1B9A" bgLvl="0" bgClr="00800080"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="006A1B9A" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1748,7 +2205,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="000F7B6C" bgLvl="0" bgClr="000A5C52"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="000F7B6C" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1759,7 +2216,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00F5F6FA"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1770,7 +2227,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00F5F6FA"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1781,7 +2238,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00FFEBEE" bgLvl="0" bgClr="00F5F6FA"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFEBEE" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1792,7 +2249,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00E8F5E9" bgLvl="0" bgClr="00EEF1F8"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E8F5E9" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1803,7 +2260,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00F5F6FA" bgLvl="0" bgClr="00EEF1F8"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00F5F6FA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1814,7 +2271,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00F5F6FA" bgLvl="0" bgClr="00EEF1F8"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00F5F6FA" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1825,7 +2282,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00FFF8E1" bgLvl="0" bgClr="00F5F6FA"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFF8E1" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1836,7 +2293,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00E3F2FD" bgLvl="0" bgClr="00EEF1F8"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E3F2FD" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1847,7 +2304,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00123A63" bgLvl="0" bgClr="00243657"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00123A63" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -1858,35 +2315,13 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="002F79C8" bgLvl="0" bgClr="001976D2"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1777598330" type="1" fgLvl="100" fgClr="00F5F6FA" bgLvl="0" bgClr="00EEF1F8"/>
+            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="002F79C8" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="22">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -1902,7 +2337,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -1921,7 +2356,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -1940,7 +2375,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -1959,7 +2394,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -1978,7 +2413,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -1997,7 +2432,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -2016,7 +2451,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -2035,7 +2470,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -2054,7 +2489,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -2073,7 +2508,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -2092,7 +2527,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -2111,7 +2546,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330">
+          <pm:border xmlns:pm="smNativeData" id="1778271503">
             <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="FFFFFF"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="0A5C52"/>
           </pm:border>
@@ -2133,7 +2568,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330">
+          <pm:border xmlns:pm="smNativeData" id="1778271503">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
@@ -2157,7 +2592,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330">
+          <pm:border xmlns:pm="smNativeData" id="1778271503">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="left" type="1" style="0" width="30" dist="20" width2="20" rgb="0F7B6C"/>
@@ -2181,7 +2616,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330">
+          <pm:border xmlns:pm="smNativeData" id="1778271503">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
@@ -2205,7 +2640,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330">
+          <pm:border xmlns:pm="smNativeData" id="1778271503">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
@@ -2229,7 +2664,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330">
+          <pm:border xmlns:pm="smNativeData" id="1778271503">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
@@ -2253,7 +2688,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330">
+          <pm:border xmlns:pm="smNativeData" id="1778271503">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="left" type="1" style="0" width="30" dist="20" width2="20" rgb="0F7B6C"/>
@@ -2277,7 +2712,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330">
+          <pm:border xmlns:pm="smNativeData" id="1778271503">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
@@ -2301,7 +2736,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330">
+          <pm:border xmlns:pm="smNativeData" id="1778271503">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
@@ -2325,7 +2760,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
@@ -2344,63 +2779,25 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1777598330"/>
+          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
         </ext>
       </extLst>
     </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="5"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2457,7 +2854,7 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2478,7 +2875,7 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2502,6 +2899,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -2511,13 +2911,140 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7" customBuiltin="1"/>
     <cellStyle name="Percent" xfId="5" builtinId="5" customBuiltin="1"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFF59E0B"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="F59E0B">
+              <pm:latin weight="bold"/>
+              <pm:cs weight="bold"/>
+              <pm:ea weight="bold"/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFF8E1" bgLvl="0" bgClr="00FFF8E1"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1976D2"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1976D2">
+              <pm:latin weight="bold"/>
+              <pm:cs weight="bold"/>
+              <pm:ea weight="bold"/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE3F2FD"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E3F2FD" bgLvl="0" bgClr="00E3F2FD"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF2E7D32"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="2E7D32">
+              <pm:latin weight="bold"/>
+              <pm:cs weight="bold"/>
+              <pm:ea weight="bold"/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E8F5E9" bgLvl="0" bgClr="00E8F5E9"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC62828"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="C62828">
+              <pm:latin weight="bold"/>
+              <pm:cs weight="bold"/>
+              <pm:ea weight="bold"/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEBEE"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFEBEE" bgLvl="0" bgClr="00FFEBEE"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF6A1B9A"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="6A1B9A">
+              <pm:latin weight="bold"/>
+              <pm:cs weight="bold"/>
+              <pm:ea weight="bold"/>
+            </pm:charSpec>
+          </ext>
+        </extLst>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFF3E5F5"/>
+          <extLst>
+            <ext uri="smNativeData">
+              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00F3E5F5" bgLvl="0" bgClr="00F3E5F5"/>
+            </ext>
+          </extLst>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1777598330" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1778271503" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1777598330" count="28">
+      <pm:colors xmlns:pm="smNativeData" id="1778271503" count="26">
         <pm:color name="Cor 24" rgb="A8B8D8"/>
         <pm:color name="Cor 25" rgb="1B2A4A"/>
         <pm:color name="Cor 26" rgb="2E7D32"/>
@@ -2529,23 +3056,21 @@
         <pm:color name="Cor 32" rgb="1976D2"/>
         <pm:color name="Cor 33" rgb="F59E0B"/>
         <pm:color name="Cor 34" rgb="243657"/>
-        <pm:color name="Cor 35" rgb="123A63"/>
-        <pm:color name="Cor 36" rgb="EEF1F8"/>
-        <pm:color name="Cor 37" rgb="F5F6FA"/>
-        <pm:color name="Cor 38" rgb="C8E6C9"/>
-        <pm:color name="Cor 39" rgb="D8DCE6"/>
-        <pm:color name="Cor 40" rgb="FFCDD2"/>
-        <pm:color name="Cor 41" rgb="E1BEE7"/>
-        <pm:color name="Cor 42" rgb="0F7B6C"/>
-        <pm:color name="Cor 43" rgb="993366"/>
-        <pm:color name="Cor 44" rgb="800080"/>
-        <pm:color name="Cor 45" rgb="0A5C52"/>
-        <pm:color name="Cor 46" rgb="FFEBEE"/>
-        <pm:color name="Cor 47" rgb="E8F5E9"/>
-        <pm:color name="Cor 48" rgb="FFF8E1"/>
-        <pm:color name="Cor 49" rgb="E3F2FD"/>
-        <pm:color name="Cor 50" rgb="2F79C8"/>
-        <pm:color name="Cor 51" rgb="FFFF9E"/>
+        <pm:color name="Cor 35" rgb="EEF1F8"/>
+        <pm:color name="Cor 36" rgb="C8E6C9"/>
+        <pm:color name="Cor 37" rgb="FFCDD2"/>
+        <pm:color name="Cor 38" rgb="E1BEE7"/>
+        <pm:color name="Cor 39" rgb="0F7B6C"/>
+        <pm:color name="Cor 40" rgb="FFEBEE"/>
+        <pm:color name="Cor 41" rgb="E8F5E9"/>
+        <pm:color name="Cor 42" rgb="F5F6FA"/>
+        <pm:color name="Cor 43" rgb="FFF8E1"/>
+        <pm:color name="Cor 44" rgb="E3F2FD"/>
+        <pm:color name="Cor 45" rgb="123A63"/>
+        <pm:color name="Cor 46" rgb="2F79C8"/>
+        <pm:color name="Cor 47" rgb="0A5C52"/>
+        <pm:color name="Cor 48" rgb="D8DCE6"/>
+        <pm:color name="Cor 49" rgb="F3E5F5"/>
       </pm:colors>
     </ext>
   </extLst>
@@ -2811,17 +3336,17 @@
   <sheetPr>
     <tabColor rgb="0F7B6C"/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr defaultRowHeight="15.40"/>
   <cols>
-    <col min="1" max="1" width="5.000000" customWidth="1" style="0"/>
-    <col min="2" max="2" width="18.000000" customWidth="1" style="0"/>
-    <col min="3" max="3" width="30.000000" customWidth="1" style="0"/>
-    <col min="4" max="4" width="36.000000" customWidth="1" style="0"/>
-    <col min="5" max="5" width="12.000000" customWidth="1" style="0"/>
-    <col min="6" max="7" width="15.000000" customWidth="1" style="0"/>
-    <col min="8" max="8" width="14.000000" customWidth="1" style="0"/>
-    <col min="9" max="9" width="28.000000" customWidth="1" style="0"/>
+    <col min="1" max="1" width="5.000000" customWidth="1"/>
+    <col min="2" max="2" width="18.000000" customWidth="1"/>
+    <col min="3" max="3" width="30.000000" customWidth="1"/>
+    <col min="4" max="4" width="36.000000" customWidth="1"/>
+    <col min="5" max="5" width="12.000000" customWidth="1"/>
+    <col min="6" max="7" width="15.000000" customWidth="1"/>
+    <col min="8" max="8" width="14.000000" customWidth="1"/>
+    <col min="9" max="9" width="28.000000" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="48" customHeight="1">
@@ -2862,19 +3387,19 @@
     </row>
     <row r="5" spans="1:9" ht="36" customHeight="1">
       <c r="A5" s="13">
-        <f>COUNTIF($A$8:$A$100,"&lt;&gt;")</f>
-        <v>68</v>
+        <f>COUNTIF($A$8:$A$97,"&lt;&gt;")</f>
+        <v>90</v>
       </c>
       <c r="C5" s="14">
-        <f>COUNTIF($F$8:$F$100,"Aprovado")</f>
+        <f>COUNTIF($F$8:$F$97,"Aprovado")</f>
         <v>66</v>
       </c>
       <c r="E5" s="15">
-        <f>COUNTIF($F$8:$F$100,"Falhou")</f>
+        <f>COUNTIF($F$8:$F$97,"Falhou")</f>
         <v>1</v>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIF($F$8:$F$100,"Bloqueado")</f>
+        <f>COUNTIF($F$8:$F$97,"Bloqueado")</f>
         <v>0</v>
       </c>
       <c r="I5" s="8"/>
@@ -4171,14 +4696,14 @@
         <v>317</v>
       </c>
       <c r="F57" s="23" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H57" s="32"/>
       <c r="I57" s="33" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="27.75" customHeight="1">
@@ -4186,22 +4711,22 @@
         <v>51</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F58" s="23" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H58" s="25"/>
       <c r="I58" s="26"/>
@@ -4211,22 +4736,22 @@
         <v>52</v>
       </c>
       <c r="B59" s="28" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C59" s="29" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F59" s="23" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="G59" s="24" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="H59" s="32"/>
       <c r="I59" s="33"/>
@@ -4236,22 +4761,22 @@
         <v>53</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F60" s="23" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="G60" s="24" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="H60" s="25"/>
       <c r="I60" s="26"/>
@@ -4261,26 +4786,26 @@
         <v>54</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="E61" s="22" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F61" s="23" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="H61" s="32"/>
       <c r="I61" s="33" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="27.75" customHeight="1">
@@ -4288,22 +4813,22 @@
         <v>55</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="E62" s="34" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="F62" s="23" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="H62" s="25"/>
       <c r="I62" s="26"/>
@@ -4313,22 +4838,22 @@
         <v>56</v>
       </c>
       <c r="B63" s="28" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C63" s="29" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="F63" s="23" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="H63" s="32"/>
       <c r="I63" s="33"/>
@@ -4338,26 +4863,26 @@
         <v>57</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="G64" s="24" t="s">
-        <v>313</v>
+        <v>363</v>
       </c>
       <c r="H64" s="25"/>
       <c r="I64" s="26" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="27.75" customHeight="1">
@@ -4365,22 +4890,22 @@
         <v>58</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="C65" s="29" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="D65" s="30" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="F65" s="23" t="s">
-        <v>312</v>
+        <v>369</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>313</v>
+        <v>370</v>
       </c>
       <c r="H65" s="32"/>
       <c r="I65" s="33"/>
@@ -4390,22 +4915,22 @@
         <v>59</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="E66" s="22" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="F66" s="23" t="s">
-        <v>312</v>
+        <v>375</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>313</v>
+        <v>376</v>
       </c>
       <c r="H66" s="25"/>
       <c r="I66" s="26"/>
@@ -4415,22 +4940,22 @@
         <v>60</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="C67" s="29" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="E67" s="22" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="F67" s="23" t="s">
-        <v>312</v>
+        <v>381</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>313</v>
+        <v>382</v>
       </c>
       <c r="H67" s="32"/>
       <c r="I67" s="33"/>
@@ -4440,22 +4965,22 @@
         <v>61</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="E68" s="22" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="F68" s="23" t="s">
-        <v>312</v>
+        <v>387</v>
       </c>
       <c r="G68" s="24" t="s">
-        <v>313</v>
+        <v>388</v>
       </c>
       <c r="H68" s="25"/>
       <c r="I68" s="26"/>
@@ -4465,22 +4990,22 @@
         <v>62</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="D69" s="30" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="E69" s="22" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="F69" s="23" t="s">
-        <v>312</v>
+        <v>393</v>
       </c>
       <c r="G69" s="24" t="s">
-        <v>313</v>
+        <v>394</v>
       </c>
       <c r="H69" s="32"/>
       <c r="I69" s="33"/>
@@ -4490,26 +5015,26 @@
         <v>63</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="E70" s="34" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="F70" s="23" t="s">
-        <v>312</v>
+        <v>399</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>313</v>
+        <v>400</v>
       </c>
       <c r="H70" s="25"/>
       <c r="I70" s="26" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="27.75" customHeight="1">
@@ -4517,22 +5042,22 @@
         <v>64</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="C71" s="29" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="F71" s="23" t="s">
-        <v>312</v>
+        <v>406</v>
       </c>
       <c r="G71" s="24" t="s">
-        <v>313</v>
+        <v>407</v>
       </c>
       <c r="H71" s="32"/>
       <c r="I71" s="33"/>
@@ -4542,22 +5067,22 @@
         <v>65</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>381</v>
+        <v>411</v>
       </c>
       <c r="F72" s="23" t="s">
-        <v>312</v>
+        <v>412</v>
       </c>
       <c r="G72" s="24" t="s">
-        <v>313</v>
+        <v>413</v>
       </c>
       <c r="H72" s="25"/>
       <c r="I72" s="26"/>
@@ -4567,22 +5092,22 @@
         <v>66</v>
       </c>
       <c r="B73" s="28" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="E73" s="22" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>312</v>
+        <v>418</v>
       </c>
       <c r="G73" s="24" t="s">
-        <v>313</v>
+        <v>419</v>
       </c>
       <c r="H73" s="32"/>
       <c r="I73" s="33"/>
@@ -4592,22 +5117,22 @@
         <v>67</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="C74" s="20" t="s">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="D74" s="21" t="s">
-        <v>388</v>
+        <v>422</v>
       </c>
       <c r="E74" s="34" t="s">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="F74" s="23" t="s">
-        <v>312</v>
+        <v>424</v>
       </c>
       <c r="G74" s="24" t="s">
-        <v>313</v>
+        <v>425</v>
       </c>
       <c r="H74" s="25"/>
       <c r="I74" s="26"/>
@@ -4617,25 +5142,531 @@
         <v>68</v>
       </c>
       <c r="B75" s="28" t="s">
-        <v>390</v>
+        <v>426</v>
       </c>
       <c r="C75" s="29" t="s">
-        <v>391</v>
+        <v>427</v>
       </c>
       <c r="D75" s="30" t="s">
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="E75" s="34" t="s">
-        <v>393</v>
+        <v>429</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>312</v>
+        <v>430</v>
       </c>
       <c r="G75" s="24" t="s">
-        <v>313</v>
+        <v>431</v>
       </c>
       <c r="H75" s="32"/>
       <c r="I75" s="33"/>
+    </row>
+    <row r="76" spans="1:9" ht="28" customHeight="1">
+      <c r="A76" s="18" t="n">
+        <v>69</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="C76" s="20" t="s">
+        <v>433</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="F76" s="40" t="s">
+        <v>436</v>
+      </c>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="26"/>
+    </row>
+    <row r="77" spans="1:9" ht="28" customHeight="1">
+      <c r="A77" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="B77" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="C77" s="29" t="s">
+        <v>438</v>
+      </c>
+      <c r="D77" s="30" t="s">
+        <v>439</v>
+      </c>
+      <c r="E77" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="F77" s="40" t="s">
+        <v>441</v>
+      </c>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
+      <c r="I77" s="33"/>
+    </row>
+    <row r="78" spans="1:9" ht="28" customHeight="1">
+      <c r="A78" s="18" t="n">
+        <v>71</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="E78" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="F78" s="40" t="s">
+        <v>446</v>
+      </c>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="26"/>
+    </row>
+    <row r="79" spans="1:9" ht="28" customHeight="1">
+      <c r="A79" s="27" t="n">
+        <v>72</v>
+      </c>
+      <c r="B79" s="28" t="s">
+        <v>447</v>
+      </c>
+      <c r="C79" s="29" t="s">
+        <v>448</v>
+      </c>
+      <c r="D79" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="F79" s="40" t="s">
+        <v>451</v>
+      </c>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="33"/>
+    </row>
+    <row r="80" spans="1:9" ht="28" customHeight="1">
+      <c r="A80" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="C80" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="E80" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="F80" s="40" t="s">
+        <v>456</v>
+      </c>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="26"/>
+    </row>
+    <row r="81" spans="1:9" ht="28" customHeight="1">
+      <c r="A81" s="27" t="n">
+        <v>74</v>
+      </c>
+      <c r="B81" s="28" t="s">
+        <v>457</v>
+      </c>
+      <c r="C81" s="29" t="s">
+        <v>458</v>
+      </c>
+      <c r="D81" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="E81" s="34" t="s">
+        <v>460</v>
+      </c>
+      <c r="F81" s="40" t="s">
+        <v>461</v>
+      </c>
+      <c r="G81" s="31"/>
+      <c r="H81" s="31"/>
+      <c r="I81" s="33"/>
+    </row>
+    <row r="82" spans="1:9" ht="28" customHeight="1">
+      <c r="A82" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="E82" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="F82" s="40" t="s">
+        <v>466</v>
+      </c>
+      <c r="G82" s="24"/>
+      <c r="H82" s="24"/>
+      <c r="I82" s="26"/>
+    </row>
+    <row r="83" spans="1:9" ht="28" customHeight="1">
+      <c r="A83" s="27" t="n">
+        <v>76</v>
+      </c>
+      <c r="B83" s="28" t="s">
+        <v>467</v>
+      </c>
+      <c r="C83" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="D83" s="30" t="s">
+        <v>469</v>
+      </c>
+      <c r="E83" s="34" t="s">
+        <v>470</v>
+      </c>
+      <c r="F83" s="40" t="s">
+        <v>471</v>
+      </c>
+      <c r="G83" s="31"/>
+      <c r="H83" s="31"/>
+      <c r="I83" s="33"/>
+    </row>
+    <row r="84" spans="1:9" ht="28" customHeight="1">
+      <c r="A84" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="C84" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="E84" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="F84" s="40" t="s">
+        <v>476</v>
+      </c>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="26"/>
+    </row>
+    <row r="85" spans="1:9" ht="28" customHeight="1">
+      <c r="A85" s="27" t="n">
+        <v>78</v>
+      </c>
+      <c r="B85" s="28" t="s">
+        <v>477</v>
+      </c>
+      <c r="C85" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="D85" s="30" t="s">
+        <v>479</v>
+      </c>
+      <c r="E85" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="F85" s="40" t="s">
+        <v>481</v>
+      </c>
+      <c r="G85" s="31"/>
+      <c r="H85" s="31"/>
+      <c r="I85" s="33"/>
+    </row>
+    <row r="86" spans="1:9" ht="28" customHeight="1">
+      <c r="A86" s="18" t="n">
+        <v>79</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>483</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>484</v>
+      </c>
+      <c r="E86" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="F86" s="40" t="s">
+        <v>486</v>
+      </c>
+      <c r="G86" s="24"/>
+      <c r="H86" s="24"/>
+      <c r="I86" s="26"/>
+    </row>
+    <row r="87" spans="1:9" ht="28" customHeight="1">
+      <c r="A87" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="B87" s="28" t="s">
+        <v>487</v>
+      </c>
+      <c r="C87" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="D87" s="30" t="s">
+        <v>489</v>
+      </c>
+      <c r="E87" s="34" t="s">
+        <v>490</v>
+      </c>
+      <c r="F87" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="G87" s="31"/>
+      <c r="H87" s="31"/>
+      <c r="I87" s="33"/>
+    </row>
+    <row r="88" spans="1:9" ht="28" customHeight="1">
+      <c r="A88" s="18" t="n">
+        <v>81</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="C88" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>494</v>
+      </c>
+      <c r="E88" s="34" t="s">
+        <v>495</v>
+      </c>
+      <c r="F88" s="40" t="s">
+        <v>496</v>
+      </c>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="26"/>
+    </row>
+    <row r="89" spans="1:9" ht="28" customHeight="1">
+      <c r="A89" s="27" t="n">
+        <v>82</v>
+      </c>
+      <c r="B89" s="28" t="s">
+        <v>497</v>
+      </c>
+      <c r="C89" s="29" t="s">
+        <v>498</v>
+      </c>
+      <c r="D89" s="30" t="s">
+        <v>499</v>
+      </c>
+      <c r="E89" s="34" t="s">
+        <v>500</v>
+      </c>
+      <c r="F89" s="40" t="s">
+        <v>501</v>
+      </c>
+      <c r="G89" s="31"/>
+      <c r="H89" s="31"/>
+      <c r="I89" s="33"/>
+    </row>
+    <row r="90" spans="1:9" ht="28" customHeight="1">
+      <c r="A90" s="18" t="n">
+        <v>83</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="E90" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="F90" s="40" t="s">
+        <v>506</v>
+      </c>
+      <c r="G90" s="24"/>
+      <c r="H90" s="24"/>
+      <c r="I90" s="26"/>
+    </row>
+    <row r="91" spans="1:9" ht="28" customHeight="1">
+      <c r="A91" s="27" t="n">
+        <v>84</v>
+      </c>
+      <c r="B91" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="C91" s="29" t="s">
+        <v>508</v>
+      </c>
+      <c r="D91" s="30" t="s">
+        <v>509</v>
+      </c>
+      <c r="E91" s="34" t="s">
+        <v>510</v>
+      </c>
+      <c r="F91" s="40" t="s">
+        <v>511</v>
+      </c>
+      <c r="G91" s="31"/>
+      <c r="H91" s="31"/>
+      <c r="I91" s="33"/>
+    </row>
+    <row r="92" spans="1:9" ht="28" customHeight="1">
+      <c r="A92" s="18" t="n">
+        <v>85</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>513</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="E92" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="F92" s="40" t="s">
+        <v>516</v>
+      </c>
+      <c r="G92" s="24"/>
+      <c r="H92" s="24"/>
+      <c r="I92" s="26"/>
+    </row>
+    <row r="93" spans="1:9" ht="28" customHeight="1">
+      <c r="A93" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="B93" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="C93" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="D93" s="30" t="s">
+        <v>519</v>
+      </c>
+      <c r="E93" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="F93" s="40" t="s">
+        <v>521</v>
+      </c>
+      <c r="G93" s="31"/>
+      <c r="H93" s="31"/>
+      <c r="I93" s="33"/>
+    </row>
+    <row r="94" spans="1:9" ht="28" customHeight="1">
+      <c r="A94" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>523</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>524</v>
+      </c>
+      <c r="E94" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="F94" s="40" t="s">
+        <v>526</v>
+      </c>
+      <c r="G94" s="24"/>
+      <c r="H94" s="24"/>
+      <c r="I94" s="26"/>
+    </row>
+    <row r="95" spans="1:9" ht="28" customHeight="1">
+      <c r="A95" s="27" t="n">
+        <v>88</v>
+      </c>
+      <c r="B95" s="28" t="s">
+        <v>527</v>
+      </c>
+      <c r="C95" s="29" t="s">
+        <v>528</v>
+      </c>
+      <c r="D95" s="30" t="s">
+        <v>529</v>
+      </c>
+      <c r="E95" s="22" t="s">
+        <v>530</v>
+      </c>
+      <c r="F95" s="40" t="s">
+        <v>531</v>
+      </c>
+      <c r="G95" s="31"/>
+      <c r="H95" s="31"/>
+      <c r="I95" s="33"/>
+    </row>
+    <row r="96" spans="1:9" ht="28" customHeight="1">
+      <c r="A96" s="18" t="n">
+        <v>89</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>533</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>534</v>
+      </c>
+      <c r="E96" s="23" t="s">
+        <v>535</v>
+      </c>
+      <c r="F96" s="40" t="s">
+        <v>536</v>
+      </c>
+      <c r="G96" s="24"/>
+      <c r="H96" s="24"/>
+      <c r="I96" s="26"/>
+    </row>
+    <row r="97" spans="1:9" ht="28" customHeight="1">
+      <c r="A97" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="B97" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="C97" s="29" t="s">
+        <v>538</v>
+      </c>
+      <c r="D97" s="30" t="s">
+        <v>539</v>
+      </c>
+      <c r="E97" s="23" t="s">
+        <v>540</v>
+      </c>
+      <c r="F97" s="40" t="s">
+        <v>541</v>
+      </c>
+      <c r="G97" s="31"/>
+      <c r="H97" s="31"/>
+      <c r="I97" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4650,8 +5681,33 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
   </mergeCells>
+  <conditionalFormatting sqref="F8:F147">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Pendente">
+      <formula>NOT(ISERROR(SEARCH("Pendente", F8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F147">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Em andamento">
+      <formula>NOT(ISERROR(SEARCH("Em andamento", F8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F147">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Aprovado">
+      <formula>NOT(ISERROR(SEARCH("Aprovado", F8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F147">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Falhou">
+      <formula>NOT(ISERROR(SEARCH("Falhou", F8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:F147">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Bloqueado">
+      <formula>NOT(ISERROR(SEARCH("Bloqueado", F8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F8:F95" type="list" operator="between" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="Status inválido" error="Selecione um status da lista." view="0">
+    <dataValidation sqref="F8:F147" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Status" prompt="Selecione o status do cenário." errorTitle="Status inválido" error="Selecione um status da lista." view="0">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
           <x12ac:list>Pendente,"Em andamento",Aprovado,Falhou,Bloqueado</x12ac:list>
@@ -4665,7 +5721,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1777598330" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1778271503" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -4674,16 +5730,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1777598330" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1777598330" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777598330" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777598330" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1778271503" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1778271503" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1778271503" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1778271503" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1777598330" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1778271503" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -4700,15 +5756,15 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.40"/>
   <cols>
-    <col min="1" max="1" width="15.000000" customWidth="1" style="0"/>
-    <col min="2" max="2" width="39.321429" customWidth="1" style="0"/>
-    <col min="4" max="4" width="12.107143" customWidth="1" style="0"/>
-    <col min="5" max="5" width="39.321429" customWidth="1" style="0"/>
+    <col min="1" max="1" width="15.000000" customWidth="1"/>
+    <col min="2" max="2" width="39.321429" customWidth="1"/>
+    <col min="4" max="4" width="12.107143" customWidth="1"/>
+    <col min="5" max="5" width="39.321429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" customHeight="1">
       <c r="A1" s="36" t="s">
-        <v>394</v>
+        <v>542</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -4718,81 +5774,81 @@
     <row r="2" spans="1:1" ht="13.80" customHeight="1"/>
     <row r="3" spans="1:5" ht="14.90" customHeight="1">
       <c r="A3" s="38" t="s">
-        <v>395</v>
+        <v>543</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>396</v>
+        <v>544</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>397</v>
+        <v>545</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>398</v>
+        <v>546</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="28.50" customHeight="1">
       <c r="A4" s="39" t="s">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>400</v>
+        <v>547</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>401</v>
+        <v>548</v>
       </c>
       <c r="E4" s="39" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.50" customHeight="1">
       <c r="A5" s="39" t="s">
-        <v>403</v>
+        <v>550</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>404</v>
+        <v>551</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>405</v>
+        <v>552</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>406</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.50" customHeight="1">
       <c r="A6" s="39" t="s">
-        <v>407</v>
+        <v>554</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>408</v>
+        <v>555</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>409</v>
+        <v>556</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>410</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28.50" customHeight="1">
       <c r="A7" s="39" t="s">
-        <v>411</v>
+        <v>558</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>412</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28.50" customHeight="1">
       <c r="A8" s="39" t="s">
-        <v>413</v>
+        <v>560</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>414</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1777598330" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1778271503" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -4801,16 +5857,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1777598330" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1777598330" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777598330" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1777598330" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1778271503" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1778271503" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1778271503" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1778271503" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1777598330" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1778271503" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/docs/homologacao/checklist_homologacao_operacional.xlsx
+++ b/docs/homologacao/checklist_homologacao_operacional.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SistemasPython\cspdv\docs\homologacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1124B1B-84A1-4B0C-833D-59354DC7E78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD7448E-92DB-4801-811B-18609A536B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
     <sheet name="Listas" sheetId="2" r:id="rId2"/>
+    <sheet name="Evidencias venda" sheetId="3" r:id="rId3"/>
+    <sheet name="Evidencias produtos" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="151">
   <si>
     <t>Checklist de Homologacao Operacional - CSPdv</t>
   </si>
@@ -444,6 +446,36 @@
   </si>
   <si>
     <t>Nao foi possivel executar por dependencia ou problema externo.</t>
+  </si>
+  <si>
+    <t>ver problemas encontrados na planlha evidencias venda</t>
+  </si>
+  <si>
+    <t>O sistema ainda não permite cadastro de usuários</t>
+  </si>
+  <si>
+    <t>Na tela de gerenciamento de produtos um duplo clique deve abrir a tela de edição.</t>
+  </si>
+  <si>
+    <t>ver evidencias e sugestões na planilha evidencias produtos</t>
+  </si>
+  <si>
+    <t>Na unidade tributável deve conter apenas a sigla da unidade, pois é essa que deverá constar na nta fiscal</t>
+  </si>
+  <si>
+    <t>Na tela de cadastro do produto, no local onde tem código auto gerado deve ser inserido o código do produto, não é o código de barras,. Esse código é fornecido pelo fabricante, na natura por exemplo esse código identifica o produto no site e nas revistas para formação do pedido</t>
+  </si>
+  <si>
+    <t>Na tela de e edição do produto, no local onde tem código auto gerado deve ser exibido o código do produto, não é o código de barras,. Esse código é fornecido pelo fabricante, na natura por exemplo esse código identifica o produto no site e nas revistas para formação do pedido</t>
+  </si>
+  <si>
+    <t>Na tela de nusca de produtos na hora da venda, ao selecionar o produto o mesmo não é inserido no cupon de venda.</t>
+  </si>
+  <si>
+    <t>Ao tentar inserir o produto pesquisado pelo nome, caso não possua disponibilidade no estoque, o sistema deve bloquear a entrada do produto no cupom, e informar que o estoque está zerado</t>
+  </si>
+  <si>
+    <t>Na busca de produtos para a venda,  o sistema deve ir exibindo a lista de produtos cadastrados a medidada que o nome for sendo digitado para que seja escolhido o produto correto.</t>
   </si>
 </sst>
 </file>
@@ -540,7 +572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -583,6 +615,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -797,7 +832,7 @@
       </c>
       <c r="B4" s="4">
         <f>COUNTIF($F$9:$F$57,"Aprovado")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C4" s="5">
         <f>COUNTIF($F$9:$F$57,"Falhou")</f>
@@ -868,7 +903,7 @@
         <v>18</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="12"/>
@@ -891,7 +926,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="12"/>
@@ -918,7 +953,9 @@
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="12"/>
-      <c r="I11" s="10"/>
+      <c r="I11" s="10" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
@@ -937,7 +974,7 @@
         <v>26</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="12"/>
@@ -960,7 +997,7 @@
         <v>18</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="12"/>
@@ -983,7 +1020,7 @@
         <v>18</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="12"/>
@@ -1010,7 +1047,9 @@
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="12"/>
-      <c r="I15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
@@ -1033,7 +1072,9 @@
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="12"/>
-      <c r="I16" s="10"/>
+      <c r="I16" s="10" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
@@ -1056,7 +1097,9 @@
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="12"/>
-      <c r="I17" s="10"/>
+      <c r="I17" s="10" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
@@ -1980,6 +2023,18 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A3B51627-5AFB-4B34-8BC5-9064D378B2FD}">
+          <x14:formula1>
+            <xm:f>Listas!$A$4:$A$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>F9:F57</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -2078,4 +2133,83 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A7AC634-7FFC-47A9-823C-E81030169370}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7ADE5CA-66CA-4E68-A853-83D3164DB9DC}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="15">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="15">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="15">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="15">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/docs/homologacao/checklist_homologacao_operacional.xlsx
+++ b/docs/homologacao/checklist_homologacao_operacional.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="iuryr"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SistemasPython\cspdv\docs\homologacao\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FDE0F1-F0D9-4B23-90C8-9BB60782298F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="16380" windowHeight="8190" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Checklist" sheetId="1" r:id="rId4"/>
-    <sheet name="Listas" sheetId="2" r:id="rId5"/>
+    <sheet name="Checklist" sheetId="1" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateDelta="0.0001"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1778271503" val="1230" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -24,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="572">
   <si>
     <t>✦  Checklist de Homologação Operacional — CSPdv</t>
   </si>
@@ -1710,376 +1715,198 @@
   </si>
   <si>
     <t>Nao foi possivel executar por dependencia ou problema externo.</t>
+  </si>
+  <si>
+    <t>Ao sair da tela sem concluir uma venda</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Ao voltar para a tela de venda, os itens acdicionados ainda devem estar disponíveis para continuar a venda</t>
+  </si>
+  <si>
+    <t>Didimo</t>
+  </si>
+  <si>
+    <t>Quando necessitar pausar uma venda</t>
+  </si>
+  <si>
+    <t>O sistema deve poder salvar como pre-venda para retornar e continuar a venda em outro momento</t>
+  </si>
+  <si>
+    <t>Implementar a solução</t>
+  </si>
+  <si>
+    <t>Ao contar e armazenar a contagem das vendas</t>
+  </si>
+  <si>
+    <t>O sistema deve armazenar apenas acontagem das vendas efetuadas</t>
+  </si>
+  <si>
+    <t>Eefetuar a correção para contabilizar apenas as vendas concluídas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;R$&quot;;\-#,##0\ &quot;R$&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;R$&quot;;[Red]\-#,##0\ &quot;R$&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;R$&quot;;\-#,##0.00\ &quot;R$&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;R$&quot;;[Red]\-#,##0.00\ &quot;R$&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;R$&quot;_-;\-* #,##0\ &quot;R$&quot;_-;_-* &quot;-&quot;\ &quot;R$&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _R_$_-;\-* #,##0\ _R_$_-;_-* &quot;-&quot;\ _R_$_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;R$&quot;_-;\-* #,##0.00\ &quot;R$&quot;_-;_-* &quot;-&quot;??\ &quot;R$&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _R_$_-;\-* #,##0.00\ _R_$_-;_-* &quot;-&quot;??\ _R_$_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-_R_$* #,##0.00_ ;_-_R_$* \-#,##0.00\ ;_-_R_$* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="165" formatCode="_-_R_$* #,##0_ ;_-_R_$* \-#,##0\ ;_-_R_$* &quot;-&quot;_ ;_-@_ "/>
-    <numFmt numFmtId="166" formatCode="_-&quot;R$&quot;* #,##0.00_ ;_-&quot;R$&quot;* \-#,##0.00\ ;_-&quot;R$&quot;* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;R$&quot;* #,##0_ ;_-&quot;R$&quot;* \-#,##0\ ;_-&quot;R$&quot;* &quot;-&quot;_ ;_-@_ "/>
-    <numFmt numFmtId="168" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="9" formatCode="0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="172" formatCode="_-_R_$* #,##0.00_ ;_-_R_$* \-#,##0.00\ ;_-_R_$* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="173" formatCode="_-_R_$* #,##0_ ;_-_R_$* \-#,##0\ ;_-_R_$* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="174" formatCode="_-&quot;R$&quot;* #,##0.00_ ;_-&quot;R$&quot;* \-#,##0.00\ ;_-&quot;R$&quot;* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="175" formatCode="_-&quot;R$&quot;* #,##0_ ;_-&quot;R$&quot;* \-#,##0\ ;_-&quot;R$&quot;* &quot;-&quot;_ ;_-@_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="320" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="320" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="320" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFA8B8D8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <i/>
-      <color rgb="FFA8B8D8"/>
-      <sz val="9"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="A8B8D8" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="180" lang="default" i="1"/>
-            <pm:cs face="Times New Roman" sz="180" lang="default" i="1"/>
-            <pm:ea face="SimSun" sz="180" lang="default" i="1"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF1B2A4A"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FF1B2A4A"/>
-      <sz val="8"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1B2A4A" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF2E7D32"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FF2E7D32"/>
-      <sz val="8"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="2E7D32" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFC62828"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FFC62828"/>
-      <sz val="8"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="C62828" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF6A1B9A"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FF6A1B9A"/>
-      <sz val="8"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="6A1B9A" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="160" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="160" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="160" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="20"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="400" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="400" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="400" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="200" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="200" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF6B7A99"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FF6B7A99"/>
-      <sz val="9"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="6B7A99" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1B2A4A"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FF1B2A4A"/>
-      <sz val="9"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1B2A4A" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF1B2A4A"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF1B2A4A"/>
-      <sz val="9"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1B2A4A" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="180" lang="default"/>
-            <pm:cs face="Times New Roman" sz="180" lang="default"/>
-            <pm:ea face="SimSun" sz="180" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF5C6880"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <i/>
-      <color rgb="FF5C6880"/>
-      <sz val="8"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="5C6880" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="160" lang="default" i="1"/>
-            <pm:cs face="Times New Roman" sz="160" lang="default" i="1"/>
-            <pm:ea face="SimSun" sz="160" lang="default" i="1"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFC62828"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FFC62828"/>
-      <sz val="9"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="C62828" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF2E7D32"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FF2E7D32"/>
-      <sz val="9"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="2E7D32" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="8"/>
+      <color rgb="FF5C6880"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF5C6880"/>
-      <sz val="8"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="5C6880" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="160" lang="default"/>
-            <pm:cs face="Times New Roman" sz="160" lang="default"/>
-            <pm:ea face="SimSun" sz="160" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFE65100"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FFE65100"/>
-      <sz val="9"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="E65100" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1976D2"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FF1976D2"/>
-      <sz val="9"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1976D2" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="260" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="260" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="260" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="FFFFFF" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="220" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFF59E0B"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b/>
-      <color rgb="FFF59E0B"/>
-      <sz val="9"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="F59E0B" ulstyle="none" kern="1">
-            <pm:latin face="Calibri" sz="180" lang="default" weight="bold"/>
-            <pm:cs face="Times New Roman" sz="180" lang="default" weight="bold"/>
-            <pm:ea face="SimSun" sz="180" lang="default" weight="bold"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
   </fonts>
   <fills count="23">
@@ -2093,465 +1920,217 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1B2A4A"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="001B2A4A" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF243657"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00243657" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF1F8"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00EEF1F8" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC8E6C9"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00C8E6C9" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCDD2"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFCDD2" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE1BEE7"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E1BEE7" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E7D32"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="002E7D32" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC62828"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00C62828" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6A1B9A"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="006A1B9A" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0F7B6C"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="000F7B6C" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEBEE"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFEBEE" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E8F5E9" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F6FA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00F5F6FA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F6FA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00F5F6FA" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF8E1"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFF8E1" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE3F2FD"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E3F2FD" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF123A63"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00123A63" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F79C8"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="002F79C8" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
   <borders count="22">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="thin">
         <color rgb="FF0A5C52"/>
       </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color rgb="FFFFFFFF"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503">
-            <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="FFFFFF"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="0A5C52"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2566,16 +2145,7 @@
       <bottom style="thin">
         <color rgb="FFD8DCE6"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -2590,16 +2160,7 @@
       <bottom style="thin">
         <color rgb="FFD8DCE6"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="left" type="1" style="0" width="30" dist="20" width2="20" rgb="0F7B6C"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2614,16 +2175,7 @@
       <bottom style="thin">
         <color rgb="FFD8DCE6"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2638,16 +2190,7 @@
       <bottom style="thin">
         <color rgb="FFD8DCE6"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2662,16 +2205,7 @@
       <bottom style="thin">
         <color rgb="FFD8DCE6"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -2686,16 +2220,7 @@
       <bottom style="thin">
         <color rgb="FFD8DCE6"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="left" type="1" style="0" width="30" dist="20" width2="20" rgb="0F7B6C"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2710,16 +2235,7 @@
       <bottom style="thin">
         <color rgb="FFD8DCE6"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2734,102 +2250,34 @@
       <bottom style="thin">
         <color rgb="FFD8DCE6"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="D8DCE6"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1778271503"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="173" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="5"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2854,7 +2302,7 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="13" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2875,7 +2323,7 @@
     <xf numFmtId="0" fontId="12" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="12" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2887,13 +2335,13 @@
     <xf numFmtId="0" fontId="18" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2902,38 +2350,77 @@
     <xf numFmtId="0" fontId="21" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
+    <cellStyle name="Moeda" xfId="3" builtinId="4" customBuiltin="1"/>
+    <cellStyle name="Moeda [0]" xfId="4" builtinId="7" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3" customBuiltin="1"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6" customBuiltin="1"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4" customBuiltin="1"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7" customBuiltin="1"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Porcentagem" xfId="5" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Separador de milhares [0]" xfId="2" builtinId="6" customBuiltin="1"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="5">
     <dxf>
       <font>
         <b/>
-        <color rgb="FFF59E0B"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="F59E0B">
-              <pm:latin weight="bold"/>
-              <pm:cs weight="bold"/>
-              <pm:ea weight="bold"/>
-            </pm:charSpec>
-          </ext>
-        </extLst>
+        <color rgb="FF6A1B9A"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFF8E1"/>
-          <extLst>
-            <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFF8E1" bgLvl="0" bgClr="00FFF8E1"/>
-            </ext>
-          </extLst>
+          <bgColor rgb="FFF3E5F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC62828"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEBEE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF2E7D32"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2941,105 +2428,33 @@
       <font>
         <b/>
         <color rgb="FF1976D2"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="1976D2">
-              <pm:latin weight="bold"/>
-              <pm:cs weight="bold"/>
-              <pm:ea weight="bold"/>
-            </pm:charSpec>
-          </ext>
-        </extLst>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFE3F2FD"/>
-          <extLst>
-            <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E3F2FD" bgLvl="0" bgClr="00E3F2FD"/>
-            </ext>
-          </extLst>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <color rgb="FF2E7D32"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="2E7D32">
-              <pm:latin weight="bold"/>
-              <pm:cs weight="bold"/>
-              <pm:ea weight="bold"/>
-            </pm:charSpec>
-          </ext>
-        </extLst>
+        <color rgb="FFF59E0B"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFE8F5E9"/>
-          <extLst>
-            <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00E8F5E9" bgLvl="0" bgClr="00E8F5E9"/>
-            </ext>
-          </extLst>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFC62828"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="C62828">
-              <pm:latin weight="bold"/>
-              <pm:cs weight="bold"/>
-              <pm:ea weight="bold"/>
-            </pm:charSpec>
-          </ext>
-        </extLst>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEBEE"/>
-          <extLst>
-            <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00FFEBEE" bgLvl="0" bgClr="00FFEBEE"/>
-            </ext>
-          </extLst>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF6A1B9A"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1778271503" fgClr="6A1B9A">
-              <pm:latin weight="bold"/>
-              <pm:cs weight="bold"/>
-              <pm:ea weight="bold"/>
-            </pm:charSpec>
-          </ext>
-        </extLst>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFF3E5F5"/>
-          <extLst>
-            <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1778271503" type="1" fgLvl="100" fgClr="00F3E5F5" bgLvl="0" bgClr="00F3E5F5"/>
-            </ext>
-          </extLst>
+          <bgColor rgb="FFFFF8E1"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1778271503" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
@@ -3332,2411 +2747,2480 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor rgb="0F7B6C"/>
+    <tabColor rgb="FF0F7B6C"/>
   </sheetPr>
-  <dimension ref="A1:I97"/>
-  <sheetFormatPr defaultRowHeight="15.40"/>
+  <dimension ref="A1:I100"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.000000" customWidth="1"/>
-    <col min="2" max="2" width="18.000000" customWidth="1"/>
-    <col min="3" max="3" width="30.000000" customWidth="1"/>
-    <col min="4" max="4" width="36.000000" customWidth="1"/>
-    <col min="5" max="5" width="12.000000" customWidth="1"/>
-    <col min="6" max="7" width="15.000000" customWidth="1"/>
-    <col min="8" max="8" width="14.000000" customWidth="1"/>
-    <col min="9" max="9" width="28.000000" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="48" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" ht="24" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+    </row>
+    <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="9.75" customHeight="1">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-    </row>
-    <row r="4" spans="1:9" ht="13.50" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+    </row>
+    <row r="3" spans="1:9" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="D4" s="27"/>
+      <c r="E4" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="F4" s="27"/>
+      <c r="G4" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="8"/>
-    </row>
-    <row r="5" spans="1:9" ht="36" customHeight="1">
-      <c r="A5" s="13">
+      <c r="H4" s="27"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33">
         <f>COUNTIF($A$8:$A$97,"&lt;&gt;")</f>
         <v>90</v>
       </c>
-      <c r="C5" s="14">
+      <c r="B5" s="27"/>
+      <c r="C5" s="34">
         <f>COUNTIF($F$8:$F$97,"Aprovado")</f>
         <v>66</v>
       </c>
-      <c r="E5" s="15">
+      <c r="D5" s="27"/>
+      <c r="E5" s="35">
         <f>COUNTIF($F$8:$F$97,"Falhou")</f>
         <v>1</v>
       </c>
-      <c r="G5" s="16">
+      <c r="F5" s="27"/>
+      <c r="G5" s="36">
         <f>COUNTIF($F$8:$F$97,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:9" ht="9.75" customHeight="1">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" ht="30" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="H5" s="27"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A8" s="18" t="n">
+    <row r="8" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>1</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="26"/>
-    </row>
-    <row r="9" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A9" s="27" t="n">
+      <c r="H8" s="10"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
         <v>2</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="32"/>
-      <c r="I9" s="33"/>
-    </row>
-    <row r="10" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A10" s="18" t="n">
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <v>3</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="25"/>
-      <c r="I10" s="26" t="s">
+      <c r="H10" s="10"/>
+      <c r="I10" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A11" s="27" t="n">
+    <row r="11" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
         <v>4</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="34" t="s">
+      <c r="E11" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="33"/>
-    </row>
-    <row r="12" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A12" s="18" t="n">
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
         <v>5</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H12" s="25"/>
-      <c r="I12" s="26"/>
-    </row>
-    <row r="13" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A13" s="27" t="n">
+      <c r="H12" s="10"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
         <v>6</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="23" t="s">
+      <c r="F13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="32"/>
-      <c r="I13" s="33"/>
-    </row>
-    <row r="14" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A14" s="18" t="n">
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
         <v>7</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="F14" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="25"/>
-      <c r="I14" s="26"/>
-    </row>
-    <row r="15" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A15" s="27" t="n">
+      <c r="H14" s="10"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
         <v>8</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H15" s="32"/>
-      <c r="I15" s="33"/>
-    </row>
-    <row r="16" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A16" s="18" t="n">
+      <c r="H15" s="17"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
         <v>9</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="25"/>
-      <c r="I16" s="26"/>
-    </row>
-    <row r="17" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A17" s="27" t="n">
+      <c r="H16" s="10"/>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12">
         <v>10</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="23" t="s">
+      <c r="F17" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="32"/>
-      <c r="I17" s="33"/>
-    </row>
-    <row r="18" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A18" s="18" t="n">
+      <c r="H17" s="17"/>
+      <c r="I17" s="18"/>
+    </row>
+    <row r="18" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
         <v>11</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F18" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="25"/>
-      <c r="I18" s="26"/>
-    </row>
-    <row r="19" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A19" s="27" t="n">
+      <c r="H18" s="10"/>
+      <c r="I18" s="11"/>
+    </row>
+    <row r="19" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
         <v>12</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="32"/>
-      <c r="I19" s="33"/>
-    </row>
-    <row r="20" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A20" s="18" t="n">
+      <c r="H19" s="17"/>
+      <c r="I19" s="18"/>
+    </row>
+    <row r="20" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
         <v>13</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="25"/>
-      <c r="I20" s="26"/>
-    </row>
-    <row r="21" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A21" s="27" t="n">
+      <c r="H20" s="10"/>
+      <c r="I20" s="11"/>
+    </row>
+    <row r="21" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
         <v>14</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="32"/>
-      <c r="I21" s="33"/>
-    </row>
-    <row r="22" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A22" s="18" t="n">
+      <c r="H21" s="17"/>
+      <c r="I21" s="18"/>
+    </row>
+    <row r="22" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
         <v>15</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="H22" s="25"/>
-      <c r="I22" s="26"/>
-    </row>
-    <row r="23" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A23" s="27" t="n">
+      <c r="H22" s="10"/>
+      <c r="I22" s="11"/>
+    </row>
+    <row r="23" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
         <v>16</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="E23" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="H23" s="32"/>
-      <c r="I23" s="33" t="s">
+      <c r="H23" s="17"/>
+      <c r="I23" s="18" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A24" s="18" t="n">
+    <row r="24" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
         <v>17</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F24" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="G24" s="24" t="s">
+      <c r="G24" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="H24" s="25"/>
-      <c r="I24" s="26"/>
-    </row>
-    <row r="25" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A25" s="27" t="n">
+      <c r="H24" s="10"/>
+      <c r="I24" s="11"/>
+    </row>
+    <row r="25" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="12">
         <v>18</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="H25" s="32"/>
-      <c r="I25" s="33" t="s">
+      <c r="H25" s="17"/>
+      <c r="I25" s="18" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A26" s="18" t="n">
+    <row r="26" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
         <v>19</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F26" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="G26" s="24" t="s">
+      <c r="G26" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="H26" s="25"/>
-      <c r="I26" s="26" t="s">
+      <c r="H26" s="10"/>
+      <c r="I26" s="11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A27" s="27" t="n">
+    <row r="27" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="12">
         <v>20</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="F27" s="35" t="s">
+      <c r="F27" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="H27" s="32"/>
-      <c r="I27" s="33"/>
-    </row>
-    <row r="28" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A28" s="18" t="n">
+      <c r="H27" s="17"/>
+      <c r="I27" s="18"/>
+    </row>
+    <row r="28" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
         <v>21</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="G28" s="24" t="s">
+      <c r="G28" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="H28" s="25"/>
-      <c r="I28" s="26"/>
-    </row>
-    <row r="29" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A29" s="27" t="n">
+      <c r="H28" s="10"/>
+      <c r="I28" s="11"/>
+    </row>
+    <row r="29" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
         <v>22</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="E29" s="34" t="s">
+      <c r="E29" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F29" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="H29" s="32"/>
-      <c r="I29" s="33"/>
-    </row>
-    <row r="30" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A30" s="18" t="n">
+      <c r="H29" s="17"/>
+      <c r="I29" s="18"/>
+    </row>
+    <row r="30" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
         <v>23</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="F30" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="G30" s="24" t="s">
+      <c r="G30" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="H30" s="25"/>
-      <c r="I30" s="26"/>
-    </row>
-    <row r="31" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A31" s="27" t="n">
+      <c r="H30" s="10"/>
+      <c r="I30" s="11"/>
+    </row>
+    <row r="31" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="12">
         <v>24</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="F31" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="H31" s="32"/>
-      <c r="I31" s="33"/>
-    </row>
-    <row r="32" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A32" s="18" t="n">
+      <c r="H31" s="17"/>
+      <c r="I31" s="18"/>
+    </row>
+    <row r="32" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
         <v>25</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="G32" s="24" t="s">
+      <c r="G32" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="H32" s="25"/>
-      <c r="I32" s="26"/>
-    </row>
-    <row r="33" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A33" s="27" t="n">
+      <c r="H32" s="10"/>
+      <c r="I32" s="11"/>
+    </row>
+    <row r="33" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="12">
         <v>26</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="D33" s="30" t="s">
+      <c r="D33" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="G33" s="31" t="s">
+      <c r="G33" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="H33" s="32"/>
-      <c r="I33" s="33"/>
-    </row>
-    <row r="34" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A34" s="18" t="n">
+      <c r="H33" s="17"/>
+      <c r="I33" s="18"/>
+    </row>
+    <row r="34" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
         <v>27</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="F34" s="23" t="s">
+      <c r="F34" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="G34" s="24" t="s">
+      <c r="G34" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="H34" s="25"/>
-      <c r="I34" s="26"/>
-    </row>
-    <row r="35" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A35" s="27" t="n">
+      <c r="H34" s="10"/>
+      <c r="I34" s="11"/>
+    </row>
+    <row r="35" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="12">
         <v>28</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="E35" s="34" t="s">
+      <c r="E35" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="F35" s="23" t="s">
+      <c r="F35" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="H35" s="32"/>
-      <c r="I35" s="33"/>
-    </row>
-    <row r="36" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A36" s="18" t="n">
+      <c r="H35" s="17"/>
+      <c r="I35" s="18"/>
+    </row>
+    <row r="36" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
         <v>29</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="F36" s="23" t="s">
+      <c r="F36" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="G36" s="24" t="s">
+      <c r="G36" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="H36" s="25"/>
-      <c r="I36" s="26"/>
-    </row>
-    <row r="37" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A37" s="27" t="n">
+      <c r="H36" s="10"/>
+      <c r="I36" s="11"/>
+    </row>
+    <row r="37" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="12">
         <v>30</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D37" s="30" t="s">
+      <c r="D37" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="F37" s="23" t="s">
+      <c r="F37" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="H37" s="32"/>
-      <c r="I37" s="33"/>
-    </row>
-    <row r="38" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A38" s="18" t="n">
+      <c r="H37" s="17"/>
+      <c r="I37" s="18"/>
+    </row>
+    <row r="38" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
         <v>31</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="F38" s="23" t="s">
+      <c r="F38" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="G38" s="24" t="s">
+      <c r="G38" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="H38" s="25"/>
-      <c r="I38" s="26"/>
-    </row>
-    <row r="39" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A39" s="27" t="n">
+      <c r="H38" s="10"/>
+      <c r="I38" s="11"/>
+    </row>
+    <row r="39" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="12">
         <v>32</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="D39" s="30" t="s">
+      <c r="D39" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="E39" s="22" t="s">
+      <c r="E39" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="H39" s="32"/>
-      <c r="I39" s="33"/>
-    </row>
-    <row r="40" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A40" s="18" t="n">
+      <c r="H39" s="17"/>
+      <c r="I39" s="18"/>
+    </row>
+    <row r="40" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
         <v>33</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="E40" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="F40" s="23" t="s">
+      <c r="F40" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="G40" s="24" t="s">
+      <c r="G40" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="H40" s="25"/>
-      <c r="I40" s="26"/>
-    </row>
-    <row r="41" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A41" s="27" t="n">
+      <c r="H40" s="10"/>
+      <c r="I40" s="11"/>
+    </row>
+    <row r="41" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="12">
         <v>34</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="D41" s="30" t="s">
+      <c r="D41" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="E41" s="22" t="s">
+      <c r="E41" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F41" s="23" t="s">
+      <c r="F41" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="H41" s="32"/>
-      <c r="I41" s="33"/>
-    </row>
-    <row r="42" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A42" s="18" t="n">
+      <c r="H41" s="17"/>
+      <c r="I41" s="18"/>
+    </row>
+    <row r="42" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
         <v>35</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B42" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D42" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="E42" s="34" t="s">
+      <c r="E42" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="F42" s="23" t="s">
+      <c r="F42" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="G42" s="24" t="s">
+      <c r="G42" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="H42" s="25"/>
-      <c r="I42" s="26"/>
-    </row>
-    <row r="43" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A43" s="27" t="n">
+      <c r="H42" s="10"/>
+      <c r="I42" s="11"/>
+    </row>
+    <row r="43" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="12">
         <v>36</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="D43" s="30" t="s">
+      <c r="D43" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="E43" s="34" t="s">
+      <c r="E43" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="F43" s="23" t="s">
+      <c r="F43" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="G43" s="31" t="s">
+      <c r="G43" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="H43" s="32"/>
-      <c r="I43" s="33"/>
-    </row>
-    <row r="44" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A44" s="18" t="n">
+      <c r="H43" s="17"/>
+      <c r="I43" s="18"/>
+    </row>
+    <row r="44" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
         <v>37</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="D44" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E44" s="22" t="s">
+      <c r="E44" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="F44" s="23" t="s">
+      <c r="F44" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="G44" s="24" t="s">
+      <c r="G44" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="H44" s="25"/>
-      <c r="I44" s="26"/>
-    </row>
-    <row r="45" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A45" s="27" t="n">
+      <c r="H44" s="10"/>
+      <c r="I44" s="11"/>
+    </row>
+    <row r="45" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="12">
         <v>38</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="D45" s="30" t="s">
+      <c r="D45" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="E45" s="22" t="s">
+      <c r="E45" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="F45" s="23" t="s">
+      <c r="F45" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="G45" s="31" t="s">
+      <c r="G45" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="H45" s="32"/>
-      <c r="I45" s="33"/>
-    </row>
-    <row r="46" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A46" s="18" t="n">
+      <c r="H45" s="17"/>
+      <c r="I45" s="18"/>
+    </row>
+    <row r="46" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
         <v>39</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="D46" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E46" s="22" t="s">
+      <c r="E46" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="F46" s="23" t="s">
+      <c r="F46" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="G46" s="24" t="s">
+      <c r="G46" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="H46" s="25"/>
-      <c r="I46" s="26"/>
-    </row>
-    <row r="47" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A47" s="27" t="n">
+      <c r="H46" s="10"/>
+      <c r="I46" s="11"/>
+    </row>
+    <row r="47" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="12">
         <v>40</v>
       </c>
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="D47" s="30" t="s">
+      <c r="D47" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="E47" s="22" t="s">
+      <c r="E47" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="F47" s="23" t="s">
+      <c r="F47" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="H47" s="32"/>
-      <c r="I47" s="33"/>
-    </row>
-    <row r="48" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A48" s="18" t="n">
+      <c r="H47" s="17"/>
+      <c r="I47" s="18"/>
+    </row>
+    <row r="48" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
         <v>41</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="F48" s="23" t="s">
+      <c r="F48" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="G48" s="24" t="s">
+      <c r="G48" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="H48" s="25"/>
-      <c r="I48" s="26"/>
-    </row>
-    <row r="49" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A49" s="27" t="n">
+      <c r="H48" s="10"/>
+      <c r="I48" s="11"/>
+    </row>
+    <row r="49" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="12">
         <v>42</v>
       </c>
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="D49" s="30" t="s">
+      <c r="D49" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="E49" s="22" t="s">
+      <c r="E49" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="F49" s="23" t="s">
+      <c r="F49" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="G49" s="31" t="s">
+      <c r="G49" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="H49" s="32"/>
-      <c r="I49" s="33"/>
-    </row>
-    <row r="50" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A50" s="18" t="n">
+      <c r="H49" s="17"/>
+      <c r="I49" s="18"/>
+    </row>
+    <row r="50" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
         <v>43</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="D50" s="21" t="s">
+      <c r="D50" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="E50" s="22" t="s">
+      <c r="E50" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="F50" s="23" t="s">
+      <c r="F50" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="G50" s="24" t="s">
+      <c r="G50" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="H50" s="25"/>
-      <c r="I50" s="26" t="s">
+      <c r="H50" s="10"/>
+      <c r="I50" s="11" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A51" s="27" t="n">
+    <row r="51" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="12">
         <v>44</v>
       </c>
-      <c r="B51" s="28" t="s">
+      <c r="B51" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="D51" s="30" t="s">
+      <c r="D51" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="E51" s="22" t="s">
+      <c r="E51" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="F51" s="23" t="s">
+      <c r="F51" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="G51" s="31" t="s">
+      <c r="G51" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="H51" s="32"/>
-      <c r="I51" s="33"/>
-    </row>
-    <row r="52" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A52" s="18" t="n">
+      <c r="H51" s="17"/>
+      <c r="I51" s="18"/>
+    </row>
+    <row r="52" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
         <v>45</v>
       </c>
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D52" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E52" s="22" t="s">
+      <c r="E52" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="F52" s="23" t="s">
+      <c r="F52" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="G52" s="24" t="s">
+      <c r="G52" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="H52" s="25"/>
-      <c r="I52" s="26"/>
-    </row>
-    <row r="53" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A53" s="27" t="n">
+      <c r="H52" s="10"/>
+      <c r="I52" s="11"/>
+    </row>
+    <row r="53" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="12">
         <v>46</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="D53" s="30" t="s">
+      <c r="D53" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="E53" s="34" t="s">
+      <c r="E53" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="F53" s="23" t="s">
+      <c r="F53" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="G53" s="31" t="s">
+      <c r="G53" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="H53" s="32"/>
-      <c r="I53" s="33"/>
-    </row>
-    <row r="54" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A54" s="18" t="n">
+      <c r="H53" s="17"/>
+      <c r="I53" s="18"/>
+    </row>
+    <row r="54" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
         <v>47</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="D54" s="21" t="s">
+      <c r="D54" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="E54" s="34" t="s">
+      <c r="E54" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="F54" s="23" t="s">
+      <c r="F54" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="G54" s="24" t="s">
+      <c r="G54" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="H54" s="25"/>
-      <c r="I54" s="26"/>
-    </row>
-    <row r="55" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A55" s="27" t="n">
+      <c r="H54" s="10"/>
+      <c r="I54" s="11"/>
+    </row>
+    <row r="55" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="12">
         <v>48</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="D55" s="30" t="s">
+      <c r="D55" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="E55" s="34" t="s">
+      <c r="E55" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="F55" s="23" t="s">
+      <c r="F55" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="G55" s="31" t="s">
+      <c r="G55" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="H55" s="32"/>
-      <c r="I55" s="33"/>
-    </row>
-    <row r="56" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A56" s="18" t="n">
+      <c r="H55" s="17"/>
+      <c r="I55" s="18"/>
+    </row>
+    <row r="56" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
         <v>49</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="B56" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C56" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="D56" s="21" t="s">
+      <c r="D56" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="E56" s="22" t="s">
+      <c r="E56" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="F56" s="23" t="s">
+      <c r="F56" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="G56" s="24" t="s">
+      <c r="G56" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="H56" s="25"/>
-      <c r="I56" s="26"/>
-    </row>
-    <row r="57" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A57" s="27" t="n">
+      <c r="H56" s="10"/>
+      <c r="I56" s="11"/>
+    </row>
+    <row r="57" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="12">
         <v>50</v>
       </c>
-      <c r="B57" s="28" t="s">
+      <c r="B57" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="D57" s="30" t="s">
+      <c r="D57" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="F57" s="23" t="s">
+      <c r="F57" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="G57" s="24" t="s">
+      <c r="G57" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="H57" s="32"/>
-      <c r="I57" s="33" t="s">
+      <c r="H57" s="17"/>
+      <c r="I57" s="18" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A58" s="18" t="n">
+    <row r="58" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
         <v>51</v>
       </c>
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="D58" s="21" t="s">
+      <c r="D58" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E58" s="22" t="s">
+      <c r="E58" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="F58" s="23" t="s">
+      <c r="F58" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="G58" s="24" t="s">
+      <c r="G58" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="H58" s="25"/>
-      <c r="I58" s="26"/>
-    </row>
-    <row r="59" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A59" s="27" t="n">
+      <c r="H58" s="10"/>
+      <c r="I58" s="11"/>
+    </row>
+    <row r="59" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="12">
         <v>52</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="D59" s="30" t="s">
+      <c r="D59" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="E59" s="22" t="s">
+      <c r="E59" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="F59" s="23" t="s">
+      <c r="F59" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="G59" s="24" t="s">
+      <c r="G59" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="H59" s="32"/>
-      <c r="I59" s="33"/>
-    </row>
-    <row r="60" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A60" s="18" t="n">
+      <c r="H59" s="17"/>
+      <c r="I59" s="18"/>
+    </row>
+    <row r="60" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
         <v>53</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="C60" s="20" t="s">
+      <c r="C60" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="D60" s="21" t="s">
+      <c r="D60" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E60" s="34" t="s">
+      <c r="E60" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="F60" s="23" t="s">
+      <c r="F60" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="G60" s="24" t="s">
+      <c r="G60" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="H60" s="25"/>
-      <c r="I60" s="26"/>
-    </row>
-    <row r="61" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A61" s="27" t="n">
+      <c r="H60" s="10"/>
+      <c r="I60" s="11"/>
+    </row>
+    <row r="61" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="12">
         <v>54</v>
       </c>
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="D61" s="30" t="s">
+      <c r="D61" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="E61" s="22" t="s">
+      <c r="E61" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="F61" s="23" t="s">
+      <c r="F61" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="G61" s="24" t="s">
+      <c r="G61" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="H61" s="32"/>
-      <c r="I61" s="33" t="s">
+      <c r="H61" s="17"/>
+      <c r="I61" s="18" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A62" s="18" t="n">
+    <row r="62" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
         <v>55</v>
       </c>
-      <c r="B62" s="19" t="s">
+      <c r="B62" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C62" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D62" s="21" t="s">
+      <c r="D62" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="E62" s="34" t="s">
+      <c r="E62" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="F62" s="23" t="s">
+      <c r="F62" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="G62" s="24" t="s">
+      <c r="G62" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="H62" s="25"/>
-      <c r="I62" s="26"/>
-    </row>
-    <row r="63" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A63" s="27" t="n">
+      <c r="H62" s="10"/>
+      <c r="I62" s="11"/>
+    </row>
+    <row r="63" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="12">
         <v>56</v>
       </c>
-      <c r="B63" s="28" t="s">
+      <c r="B63" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="D63" s="30" t="s">
+      <c r="D63" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E63" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F63" s="23" t="s">
+      <c r="F63" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="G63" s="24" t="s">
+      <c r="G63" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="H63" s="32"/>
-      <c r="I63" s="33"/>
-    </row>
-    <row r="64" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A64" s="18" t="n">
+      <c r="H63" s="17"/>
+      <c r="I63" s="18"/>
+    </row>
+    <row r="64" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
         <v>57</v>
       </c>
-      <c r="B64" s="19" t="s">
+      <c r="B64" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="D64" s="21" t="s">
+      <c r="D64" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E64" s="22" t="s">
+      <c r="E64" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="F64" s="23" t="s">
+      <c r="F64" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="G64" s="24" t="s">
+      <c r="G64" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="H64" s="25"/>
-      <c r="I64" s="26" t="s">
+      <c r="H64" s="10"/>
+      <c r="I64" s="11" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A65" s="27" t="n">
+    <row r="65" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="12">
         <v>58</v>
       </c>
-      <c r="B65" s="28" t="s">
+      <c r="B65" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="D65" s="30" t="s">
+      <c r="D65" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="F65" s="23" t="s">
+      <c r="F65" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="G65" s="24" t="s">
+      <c r="G65" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="H65" s="32"/>
-      <c r="I65" s="33"/>
-    </row>
-    <row r="66" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A66" s="18" t="n">
+      <c r="H65" s="17"/>
+      <c r="I65" s="18"/>
+    </row>
+    <row r="66" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3">
         <v>59</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="B66" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="D66" s="21" t="s">
+      <c r="D66" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="F66" s="23" t="s">
+      <c r="F66" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G66" s="24" t="s">
+      <c r="G66" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="H66" s="25"/>
-      <c r="I66" s="26"/>
-    </row>
-    <row r="67" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A67" s="27" t="n">
+      <c r="H66" s="10"/>
+      <c r="I66" s="11"/>
+    </row>
+    <row r="67" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="12">
         <v>60</v>
       </c>
-      <c r="B67" s="28" t="s">
+      <c r="B67" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="D67" s="30" t="s">
+      <c r="D67" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="F67" s="23" t="s">
+      <c r="F67" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="G67" s="24" t="s">
+      <c r="G67" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="H67" s="32"/>
-      <c r="I67" s="33"/>
-    </row>
-    <row r="68" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A68" s="18" t="n">
+      <c r="H67" s="17"/>
+      <c r="I67" s="18"/>
+    </row>
+    <row r="68" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="3">
         <v>61</v>
       </c>
-      <c r="B68" s="19" t="s">
+      <c r="B68" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="C68" s="20" t="s">
+      <c r="C68" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="D68" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="E68" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="F68" s="23" t="s">
+      <c r="F68" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="G68" s="24" t="s">
+      <c r="G68" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="H68" s="25"/>
-      <c r="I68" s="26"/>
-    </row>
-    <row r="69" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A69" s="27" t="n">
+      <c r="H68" s="10"/>
+      <c r="I68" s="11"/>
+    </row>
+    <row r="69" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="12">
         <v>62</v>
       </c>
-      <c r="B69" s="28" t="s">
+      <c r="B69" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="D69" s="30" t="s">
+      <c r="D69" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="E69" s="22" t="s">
+      <c r="E69" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="F69" s="23" t="s">
+      <c r="F69" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="G69" s="24" t="s">
+      <c r="G69" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="H69" s="32"/>
-      <c r="I69" s="33"/>
-    </row>
-    <row r="70" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A70" s="18" t="n">
+      <c r="H69" s="17"/>
+      <c r="I69" s="18"/>
+    </row>
+    <row r="70" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
         <v>63</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="B70" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="C70" s="20" t="s">
+      <c r="C70" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="D70" s="21" t="s">
+      <c r="D70" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="E70" s="34" t="s">
+      <c r="E70" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="F70" s="23" t="s">
+      <c r="F70" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="G70" s="24" t="s">
+      <c r="G70" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="H70" s="25"/>
-      <c r="I70" s="26" t="s">
+      <c r="H70" s="10"/>
+      <c r="I70" s="11" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A71" s="27" t="n">
+    <row r="71" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="12">
         <v>64</v>
       </c>
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="D71" s="30" t="s">
+      <c r="D71" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="E71" s="22" t="s">
+      <c r="E71" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="F71" s="23" t="s">
+      <c r="F71" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="G71" s="24" t="s">
+      <c r="G71" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="H71" s="32"/>
-      <c r="I71" s="33"/>
-    </row>
-    <row r="72" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A72" s="18" t="n">
+      <c r="H71" s="17"/>
+      <c r="I71" s="18"/>
+    </row>
+    <row r="72" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3">
         <v>65</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B72" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="D72" s="21" t="s">
+      <c r="D72" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="E72" s="22" t="s">
+      <c r="E72" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="F72" s="23" t="s">
+      <c r="F72" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="G72" s="24" t="s">
+      <c r="G72" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="H72" s="25"/>
-      <c r="I72" s="26"/>
-    </row>
-    <row r="73" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A73" s="27" t="n">
+      <c r="H72" s="10"/>
+      <c r="I72" s="11"/>
+    </row>
+    <row r="73" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="12">
         <v>66</v>
       </c>
-      <c r="B73" s="28" t="s">
+      <c r="B73" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="D73" s="30" t="s">
+      <c r="D73" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="E73" s="22" t="s">
+      <c r="E73" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="F73" s="23" t="s">
+      <c r="F73" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="G73" s="24" t="s">
+      <c r="G73" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="H73" s="32"/>
-      <c r="I73" s="33"/>
-    </row>
-    <row r="74" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A74" s="18" t="n">
+      <c r="H73" s="17"/>
+      <c r="I73" s="18"/>
+    </row>
+    <row r="74" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3">
         <v>67</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B74" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="C74" s="20" t="s">
+      <c r="C74" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="D74" s="21" t="s">
+      <c r="D74" s="6" t="s">
         <v>422</v>
       </c>
-      <c r="E74" s="34" t="s">
+      <c r="E74" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="F74" s="23" t="s">
+      <c r="F74" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="G74" s="24" t="s">
+      <c r="G74" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="H74" s="25"/>
-      <c r="I74" s="26"/>
-    </row>
-    <row r="75" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A75" s="27" t="n">
+      <c r="H74" s="10"/>
+      <c r="I74" s="11"/>
+    </row>
+    <row r="75" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="12">
         <v>68</v>
       </c>
-      <c r="B75" s="28" t="s">
+      <c r="B75" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="D75" s="30" t="s">
+      <c r="D75" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="E75" s="34" t="s">
+      <c r="E75" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="F75" s="23" t="s">
+      <c r="F75" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="G75" s="24" t="s">
+      <c r="G75" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="H75" s="32"/>
-      <c r="I75" s="33"/>
-    </row>
-    <row r="76" spans="1:9" ht="28" customHeight="1">
-      <c r="A76" s="18" t="n">
+      <c r="H75" s="17"/>
+      <c r="I75" s="18"/>
+    </row>
+    <row r="76" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="3">
         <v>69</v>
       </c>
-      <c r="B76" s="19" t="s">
+      <c r="B76" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="C76" s="20" t="s">
+      <c r="C76" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="D76" s="21" t="s">
+      <c r="D76" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="E76" s="22" t="s">
+      <c r="E76" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="F76" s="40" t="s">
+      <c r="F76" s="25" t="s">
         <v>436</v>
       </c>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="26"/>
-    </row>
-    <row r="77" spans="1:9" ht="28" customHeight="1">
-      <c r="A77" s="27" t="n">
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="11"/>
+    </row>
+    <row r="77" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="12">
         <v>70</v>
       </c>
-      <c r="B77" s="28" t="s">
+      <c r="B77" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="D77" s="30" t="s">
+      <c r="D77" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="E77" s="22" t="s">
+      <c r="E77" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="F77" s="40" t="s">
+      <c r="F77" s="25" t="s">
         <v>441</v>
       </c>
-      <c r="G77" s="31"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="33"/>
-    </row>
-    <row r="78" spans="1:9" ht="28" customHeight="1">
-      <c r="A78" s="18" t="n">
+      <c r="G77" s="16"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="18"/>
+    </row>
+    <row r="78" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3">
         <v>71</v>
       </c>
-      <c r="B78" s="19" t="s">
+      <c r="B78" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="C78" s="20" t="s">
+      <c r="C78" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="D78" s="21" t="s">
+      <c r="D78" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="E78" s="34" t="s">
+      <c r="E78" s="19" t="s">
         <v>445</v>
       </c>
-      <c r="F78" s="40" t="s">
+      <c r="F78" s="25" t="s">
         <v>446</v>
       </c>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="26"/>
-    </row>
-    <row r="79" spans="1:9" ht="28" customHeight="1">
-      <c r="A79" s="27" t="n">
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="11"/>
+    </row>
+    <row r="79" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="12">
         <v>72</v>
       </c>
-      <c r="B79" s="28" t="s">
+      <c r="B79" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="D79" s="30" t="s">
+      <c r="D79" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="E79" s="22" t="s">
+      <c r="E79" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="F79" s="40" t="s">
+      <c r="F79" s="25" t="s">
         <v>451</v>
       </c>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="33"/>
-    </row>
-    <row r="80" spans="1:9" ht="28" customHeight="1">
-      <c r="A80" s="18" t="n">
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="18"/>
+    </row>
+    <row r="80" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3">
         <v>73</v>
       </c>
-      <c r="B80" s="19" t="s">
+      <c r="B80" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="C80" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D80" s="21" t="s">
+      <c r="D80" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="E80" s="22" t="s">
+      <c r="E80" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="F80" s="40" t="s">
+      <c r="F80" s="25" t="s">
         <v>456</v>
       </c>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="26"/>
-    </row>
-    <row r="81" spans="1:9" ht="28" customHeight="1">
-      <c r="A81" s="27" t="n">
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
+      <c r="I80" s="11"/>
+    </row>
+    <row r="81" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="12">
         <v>74</v>
       </c>
-      <c r="B81" s="28" t="s">
+      <c r="B81" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="D81" s="30" t="s">
+      <c r="D81" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="E81" s="34" t="s">
+      <c r="E81" s="19" t="s">
         <v>460</v>
       </c>
-      <c r="F81" s="40" t="s">
+      <c r="F81" s="25" t="s">
         <v>461</v>
       </c>
-      <c r="G81" s="31"/>
-      <c r="H81" s="31"/>
-      <c r="I81" s="33"/>
-    </row>
-    <row r="82" spans="1:9" ht="28" customHeight="1">
-      <c r="A82" s="18" t="n">
+      <c r="G81" s="16"/>
+      <c r="H81" s="16"/>
+      <c r="I81" s="18"/>
+    </row>
+    <row r="82" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="3">
         <v>75</v>
       </c>
-      <c r="B82" s="19" t="s">
+      <c r="B82" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="C82" s="20" t="s">
+      <c r="C82" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="D82" s="21" t="s">
+      <c r="D82" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="E82" s="22" t="s">
+      <c r="E82" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="F82" s="40" t="s">
+      <c r="F82" s="25" t="s">
         <v>466</v>
       </c>
-      <c r="G82" s="24"/>
-      <c r="H82" s="24"/>
-      <c r="I82" s="26"/>
-    </row>
-    <row r="83" spans="1:9" ht="28" customHeight="1">
-      <c r="A83" s="27" t="n">
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="11"/>
+    </row>
+    <row r="83" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="12">
         <v>76</v>
       </c>
-      <c r="B83" s="28" t="s">
+      <c r="B83" s="13" t="s">
         <v>467</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="D83" s="30" t="s">
+      <c r="D83" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="E83" s="34" t="s">
+      <c r="E83" s="19" t="s">
         <v>470</v>
       </c>
-      <c r="F83" s="40" t="s">
+      <c r="F83" s="25" t="s">
         <v>471</v>
       </c>
-      <c r="G83" s="31"/>
-      <c r="H83" s="31"/>
-      <c r="I83" s="33"/>
-    </row>
-    <row r="84" spans="1:9" ht="28" customHeight="1">
-      <c r="A84" s="18" t="n">
+      <c r="G83" s="16"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="18"/>
+    </row>
+    <row r="84" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3">
         <v>77</v>
       </c>
-      <c r="B84" s="19" t="s">
+      <c r="B84" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="C84" s="20" t="s">
+      <c r="C84" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="D84" s="21" t="s">
+      <c r="D84" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="E84" s="22" t="s">
+      <c r="E84" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="F84" s="40" t="s">
+      <c r="F84" s="25" t="s">
         <v>476</v>
       </c>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="26"/>
-    </row>
-    <row r="85" spans="1:9" ht="28" customHeight="1">
-      <c r="A85" s="27" t="n">
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
+      <c r="I84" s="11"/>
+    </row>
+    <row r="85" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="12">
         <v>78</v>
       </c>
-      <c r="B85" s="28" t="s">
+      <c r="B85" s="13" t="s">
         <v>477</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="D85" s="30" t="s">
+      <c r="D85" s="15" t="s">
         <v>479</v>
       </c>
-      <c r="E85" s="22" t="s">
+      <c r="E85" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="F85" s="40" t="s">
+      <c r="F85" s="25" t="s">
         <v>481</v>
       </c>
-      <c r="G85" s="31"/>
-      <c r="H85" s="31"/>
-      <c r="I85" s="33"/>
-    </row>
-    <row r="86" spans="1:9" ht="28" customHeight="1">
-      <c r="A86" s="18" t="n">
+      <c r="G85" s="16"/>
+      <c r="H85" s="16"/>
+      <c r="I85" s="18"/>
+    </row>
+    <row r="86" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="3">
         <v>79</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B86" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="C86" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="D86" s="21" t="s">
+      <c r="D86" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="E86" s="22" t="s">
+      <c r="E86" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="F86" s="40" t="s">
+      <c r="F86" s="25" t="s">
         <v>486</v>
       </c>
-      <c r="G86" s="24"/>
-      <c r="H86" s="24"/>
-      <c r="I86" s="26"/>
-    </row>
-    <row r="87" spans="1:9" ht="28" customHeight="1">
-      <c r="A87" s="27" t="n">
+      <c r="G86" s="9"/>
+      <c r="H86" s="9"/>
+      <c r="I86" s="11"/>
+    </row>
+    <row r="87" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="12">
         <v>80</v>
       </c>
-      <c r="B87" s="28" t="s">
+      <c r="B87" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="C87" s="29" t="s">
+      <c r="C87" s="14" t="s">
         <v>488</v>
       </c>
-      <c r="D87" s="30" t="s">
+      <c r="D87" s="15" t="s">
         <v>489</v>
       </c>
-      <c r="E87" s="34" t="s">
+      <c r="E87" s="19" t="s">
         <v>490</v>
       </c>
-      <c r="F87" s="40" t="s">
+      <c r="F87" s="25" t="s">
         <v>491</v>
       </c>
-      <c r="G87" s="31"/>
-      <c r="H87" s="31"/>
-      <c r="I87" s="33"/>
-    </row>
-    <row r="88" spans="1:9" ht="28" customHeight="1">
-      <c r="A88" s="18" t="n">
+      <c r="G87" s="16"/>
+      <c r="H87" s="16"/>
+      <c r="I87" s="18"/>
+    </row>
+    <row r="88" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3">
         <v>81</v>
       </c>
-      <c r="B88" s="19" t="s">
+      <c r="B88" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="D88" s="21" t="s">
+      <c r="D88" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="E88" s="34" t="s">
+      <c r="E88" s="19" t="s">
         <v>495</v>
       </c>
-      <c r="F88" s="40" t="s">
+      <c r="F88" s="25" t="s">
         <v>496</v>
       </c>
-      <c r="G88" s="24"/>
-      <c r="H88" s="24"/>
-      <c r="I88" s="26"/>
-    </row>
-    <row r="89" spans="1:9" ht="28" customHeight="1">
-      <c r="A89" s="27" t="n">
+      <c r="G88" s="9"/>
+      <c r="H88" s="9"/>
+      <c r="I88" s="11"/>
+    </row>
+    <row r="89" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="12">
         <v>82</v>
       </c>
-      <c r="B89" s="28" t="s">
+      <c r="B89" s="13" t="s">
         <v>497</v>
       </c>
-      <c r="C89" s="29" t="s">
+      <c r="C89" s="14" t="s">
         <v>498</v>
       </c>
-      <c r="D89" s="30" t="s">
+      <c r="D89" s="15" t="s">
         <v>499</v>
       </c>
-      <c r="E89" s="34" t="s">
+      <c r="E89" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="F89" s="40" t="s">
+      <c r="F89" s="25" t="s">
         <v>501</v>
       </c>
-      <c r="G89" s="31"/>
-      <c r="H89" s="31"/>
-      <c r="I89" s="33"/>
-    </row>
-    <row r="90" spans="1:9" ht="28" customHeight="1">
-      <c r="A90" s="18" t="n">
+      <c r="G89" s="16"/>
+      <c r="H89" s="16"/>
+      <c r="I89" s="18"/>
+    </row>
+    <row r="90" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="3">
         <v>83</v>
       </c>
-      <c r="B90" s="19" t="s">
+      <c r="B90" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="C90" s="20" t="s">
+      <c r="C90" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="D90" s="21" t="s">
+      <c r="D90" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="E90" s="22" t="s">
+      <c r="E90" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="F90" s="40" t="s">
+      <c r="F90" s="25" t="s">
         <v>506</v>
       </c>
-      <c r="G90" s="24"/>
-      <c r="H90" s="24"/>
-      <c r="I90" s="26"/>
-    </row>
-    <row r="91" spans="1:9" ht="28" customHeight="1">
-      <c r="A91" s="27" t="n">
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
+      <c r="I90" s="11"/>
+    </row>
+    <row r="91" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="12">
         <v>84</v>
       </c>
-      <c r="B91" s="28" t="s">
+      <c r="B91" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="C91" s="29" t="s">
+      <c r="C91" s="14" t="s">
         <v>508</v>
       </c>
-      <c r="D91" s="30" t="s">
+      <c r="D91" s="15" t="s">
         <v>509</v>
       </c>
-      <c r="E91" s="34" t="s">
+      <c r="E91" s="19" t="s">
         <v>510</v>
       </c>
-      <c r="F91" s="40" t="s">
+      <c r="F91" s="25" t="s">
         <v>511</v>
       </c>
-      <c r="G91" s="31"/>
-      <c r="H91" s="31"/>
-      <c r="I91" s="33"/>
-    </row>
-    <row r="92" spans="1:9" ht="28" customHeight="1">
-      <c r="A92" s="18" t="n">
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="18"/>
+    </row>
+    <row r="92" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="3">
         <v>85</v>
       </c>
-      <c r="B92" s="19" t="s">
+      <c r="B92" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="C92" s="20" t="s">
+      <c r="C92" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="D92" s="21" t="s">
+      <c r="D92" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="E92" s="22" t="s">
+      <c r="E92" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="F92" s="40" t="s">
+      <c r="F92" s="25" t="s">
         <v>516</v>
       </c>
-      <c r="G92" s="24"/>
-      <c r="H92" s="24"/>
-      <c r="I92" s="26"/>
-    </row>
-    <row r="93" spans="1:9" ht="28" customHeight="1">
-      <c r="A93" s="27" t="n">
+      <c r="G92" s="9"/>
+      <c r="H92" s="9"/>
+      <c r="I92" s="11"/>
+    </row>
+    <row r="93" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="12">
         <v>86</v>
       </c>
-      <c r="B93" s="28" t="s">
+      <c r="B93" s="13" t="s">
         <v>517</v>
       </c>
-      <c r="C93" s="29" t="s">
+      <c r="C93" s="14" t="s">
         <v>518</v>
       </c>
-      <c r="D93" s="30" t="s">
+      <c r="D93" s="15" t="s">
         <v>519</v>
       </c>
-      <c r="E93" s="34" t="s">
+      <c r="E93" s="19" t="s">
         <v>520</v>
       </c>
-      <c r="F93" s="40" t="s">
+      <c r="F93" s="25" t="s">
         <v>521</v>
       </c>
-      <c r="G93" s="31"/>
-      <c r="H93" s="31"/>
-      <c r="I93" s="33"/>
-    </row>
-    <row r="94" spans="1:9" ht="28" customHeight="1">
-      <c r="A94" s="18" t="n">
+      <c r="G93" s="16"/>
+      <c r="H93" s="16"/>
+      <c r="I93" s="18"/>
+    </row>
+    <row r="94" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="3">
         <v>87</v>
       </c>
-      <c r="B94" s="19" t="s">
+      <c r="B94" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="C94" s="20" t="s">
+      <c r="C94" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="D94" s="21" t="s">
+      <c r="D94" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="E94" s="23" t="s">
+      <c r="E94" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="F94" s="40" t="s">
+      <c r="F94" s="25" t="s">
         <v>526</v>
       </c>
-      <c r="G94" s="24"/>
-      <c r="H94" s="24"/>
-      <c r="I94" s="26"/>
-    </row>
-    <row r="95" spans="1:9" ht="28" customHeight="1">
-      <c r="A95" s="27" t="n">
+      <c r="G94" s="9"/>
+      <c r="H94" s="9"/>
+      <c r="I94" s="11"/>
+    </row>
+    <row r="95" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="12">
         <v>88</v>
       </c>
-      <c r="B95" s="28" t="s">
+      <c r="B95" s="13" t="s">
         <v>527</v>
       </c>
-      <c r="C95" s="29" t="s">
+      <c r="C95" s="14" t="s">
         <v>528</v>
       </c>
-      <c r="D95" s="30" t="s">
+      <c r="D95" s="15" t="s">
         <v>529</v>
       </c>
-      <c r="E95" s="22" t="s">
+      <c r="E95" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="F95" s="40" t="s">
+      <c r="F95" s="25" t="s">
         <v>531</v>
       </c>
-      <c r="G95" s="31"/>
-      <c r="H95" s="31"/>
-      <c r="I95" s="33"/>
-    </row>
-    <row r="96" spans="1:9" ht="28" customHeight="1">
-      <c r="A96" s="18" t="n">
+      <c r="G95" s="16"/>
+      <c r="H95" s="16"/>
+      <c r="I95" s="18"/>
+    </row>
+    <row r="96" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="3">
         <v>89</v>
       </c>
-      <c r="B96" s="19" t="s">
+      <c r="B96" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="C96" s="20" t="s">
+      <c r="C96" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="D96" s="21" t="s">
+      <c r="D96" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="E96" s="23" t="s">
+      <c r="E96" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="F96" s="40" t="s">
+      <c r="F96" s="25" t="s">
         <v>536</v>
       </c>
-      <c r="G96" s="24"/>
-      <c r="H96" s="24"/>
-      <c r="I96" s="26"/>
-    </row>
-    <row r="97" spans="1:9" ht="28" customHeight="1">
-      <c r="A97" s="27" t="n">
+      <c r="G96" s="9"/>
+      <c r="H96" s="9"/>
+      <c r="I96" s="11"/>
+    </row>
+    <row r="97" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="12">
         <v>90</v>
       </c>
-      <c r="B97" s="28" t="s">
+      <c r="B97" s="13" t="s">
         <v>537</v>
       </c>
-      <c r="C97" s="29" t="s">
+      <c r="C97" s="14" t="s">
         <v>538</v>
       </c>
-      <c r="D97" s="30" t="s">
+      <c r="D97" s="15" t="s">
         <v>539</v>
       </c>
-      <c r="E97" s="23" t="s">
+      <c r="E97" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="F97" s="40" t="s">
+      <c r="F97" s="25" t="s">
         <v>541</v>
       </c>
-      <c r="G97" s="31"/>
-      <c r="H97" s="31"/>
-      <c r="I97" s="33"/>
+      <c r="G97" s="16"/>
+      <c r="H97" s="16"/>
+      <c r="I97" s="18"/>
+    </row>
+    <row r="98" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="3">
+        <v>91</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="F98" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="H98" s="9"/>
+      <c r="I98" s="11" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="12"/>
+      <c r="B99" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="F99" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="G99" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="H99" s="16"/>
+      <c r="I99" s="18" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="3"/>
+      <c r="B100" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="F100" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="H100" s="9"/>
+      <c r="I100" s="11" t="s">
+        <v>571</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <conditionalFormatting sqref="F8:F147">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Pendente">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Pendente">
       <formula>NOT(ISERROR(SEARCH("Pendente", F8)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F147">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Em andamento">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Em andamento">
       <formula>NOT(ISERROR(SEARCH("Em andamento", F8)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F147">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Aprovado">
       <formula>NOT(ISERROR(SEARCH("Aprovado", F8)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F147">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Falhou">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Falhou">
       <formula>NOT(ISERROR(SEARCH("Falhou", F8)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F147">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Bloqueado">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Bloqueado">
       <formula>NOT(ISERROR(SEARCH("Bloqueado", F8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F8:F147" type="list" operator="between" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Status" prompt="Selecione o status do cenário." errorTitle="Status inválido" error="Selecione um status da lista." view="0">
-      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x12ac">
-          <x12ac:list>Pendente,"Em andamento",Aprovado,Falhou,Bloqueado</x12ac:list>
-        </mc:Choice>
-        <mc:Fallback>
-          <formula1>"Pendente,Em andamento,Aprovado,Falhou,Bloqueado"</formula1>
-        </mc:Fallback>
-      </mc:AlternateContent>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Status inválido" error="Selecione um status da lista." promptTitle="Status" prompt="Selecione o status do cenário." sqref="F8:F147" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Pendente,Em andamento,Aprovado,Falhou,Bloqueado"</formula1>
     </dataValidation>
   </dataValidations>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1778271503" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.511806" footer="0.511806"/>
-  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="1" pageOrder="overThenDown"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1778271503" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1778271503" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1778271503" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1778271503" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180599999999998" footer="0.51180599999999998"/>
+  <pageSetup paperSize="9" pageOrder="overThenDown"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1778271503" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
@@ -5749,121 +5233,104 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="1B2A4A"/>
+    <tabColor rgb="FF1B2A4A"/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15.40"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.000000" customWidth="1"/>
-    <col min="2" max="2" width="39.321429" customWidth="1"/>
-    <col min="4" max="4" width="12.107143" customWidth="1"/>
-    <col min="5" max="5" width="39.321429" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
+    <col min="5" max="5" width="39.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>542</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-    </row>
-    <row r="2" spans="1:1" ht="13.80" customHeight="1"/>
-    <row r="3" spans="1:5" ht="14.90" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+    </row>
+    <row r="2" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:5" ht="14.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
         <v>543</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="23" t="s">
         <v>544</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="23" t="s">
         <v>545</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="23" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.50" customHeight="1">
-      <c r="A4" s="39" t="s">
+    <row r="4" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>436</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="24" t="s">
         <v>547</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="24" t="s">
         <v>548</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="24" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.50" customHeight="1">
-      <c r="A5" s="39" t="s">
+    <row r="5" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="24" t="s">
         <v>550</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="24" t="s">
         <v>551</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="24" t="s">
         <v>552</v>
       </c>
-      <c r="E5" s="39" t="s">
+      <c r="E5" s="24" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.50" customHeight="1">
-      <c r="A6" s="39" t="s">
+    <row r="6" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
         <v>554</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="24" t="s">
         <v>555</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="24" t="s">
         <v>556</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="24" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.50" customHeight="1">
-      <c r="A7" s="39" t="s">
+    <row r="7" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
         <v>558</v>
       </c>
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="24" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="28.50" customHeight="1">
-      <c r="A8" s="39" t="s">
+    <row r="8" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
         <v>560</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="24" t="s">
         <v>561</v>
       </c>
     </row>
   </sheetData>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1778271503" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.511806" footer="0.511806"/>
-  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="1" pageOrder="overThenDown"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1778271503" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1778271503" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1778271503" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1778271503" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180599999999998" footer="0.51180599999999998"/>
+  <pageSetup paperSize="9" pageOrder="overThenDown"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1778271503" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
